--- a/docs/xlsx/jobs-2026-10-16.xlsx
+++ b/docs/xlsx/jobs-2026-10-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="588">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1753 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Animal Care and Education Intern</t>
+  </si>
+  <si>
+    <t>Calusa Nature Center and Planetarium</t>
+  </si>
+  <si>
+    <t>Fort Myers, FL</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t>environmental-education-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-animal-care-and-education-intern-fort-myers-florida/5857399957</t>
+  </si>
+  <si>
+    <t>Archaeologist</t>
+  </si>
+  <si>
+    <t>NEW Solutions</t>
+  </si>
+  <si>
+    <t>Big Bend National Park, TX</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$40 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-archaeologist-big-bend-national-park-texas/9169303203</t>
+  </si>
+  <si>
+    <t>Arizona – New Mexico Director</t>
+  </si>
+  <si>
+    <t>Western Watersheds Project</t>
+  </si>
+  <si>
+    <t>Tucson, AZ</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$84,916 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-arizona--new-mexico-director-tucson-arizona/9917645507</t>
+  </si>
+  <si>
+    <t>Camp Counselor</t>
+  </si>
+  <si>
+    <t>Eagle's Nest Camp</t>
+  </si>
+  <si>
+    <t>Pisgah Forst, NC</t>
+  </si>
+  <si>
+    <t>$315 - $350 per week</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-camp-counselor-pisgah-forst-north-carolina/8769826004</t>
+  </si>
+  <si>
+    <t>Conservation Director</t>
+  </si>
+  <si>
+    <t>Hispanic Access Foundation</t>
+  </si>
+  <si>
+    <t>Washington, DC, Remote</t>
+  </si>
+  <si>
+    <t>$100,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-director-washington-dc-remote/9449908655</t>
+  </si>
+  <si>
+    <t>Conservation Intern</t>
+  </si>
+  <si>
+    <t>Sea Turtle Inc</t>
+  </si>
+  <si>
+    <t>South Padre Island, TX</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$35 per day</t>
+  </si>
+  <si>
+    <t>marine-biology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-intern-south-padre-island-texas/7560124205</t>
+  </si>
+  <si>
+    <t>Conservation Specialist</t>
+  </si>
+  <si>
+    <t>Manistee Conservation District</t>
+  </si>
+  <si>
+    <t>Bear Lake, MI</t>
+  </si>
+  <si>
+    <t>$45,000 - $54,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-specialist-bear-lake-michigan/3149292226</t>
+  </si>
+  <si>
+    <t>Development and Administrative Associate</t>
+  </si>
+  <si>
+    <t>Forest Society of Maine</t>
+  </si>
+  <si>
+    <t>Bangor, ME</t>
+  </si>
+  <si>
+    <t>$45,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-and-administrative-associate-bangor-maine/4604251059</t>
+  </si>
+  <si>
+    <t>Education Intern</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-intern-fort-myers-florida/1080839914</t>
+  </si>
+  <si>
+    <t>Education Internship</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-internship-south-padre-island-texas/3391162158</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>The Kennebec Land Trust</t>
+  </si>
+  <si>
+    <t>Winthrop, ME</t>
+  </si>
+  <si>
+    <t>$87,000 - $106,200 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-winthrop-maine/9262620442</t>
+  </si>
+  <si>
+    <t>Field Supervisor/Project Manager</t>
+  </si>
+  <si>
+    <t>The Wetlandsbank Company</t>
+  </si>
+  <si>
+    <t>Naples, FL</t>
+  </si>
+  <si>
+    <t>$60,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-supervisorproject-manager-naples-florida/4599796752</t>
+  </si>
+  <si>
+    <t>Forest Nursery Technician</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$44,856 - $59,760 per year</t>
+  </si>
+  <si>
+    <t>botany-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-nursery-technician-olympia-washington/3223799387</t>
+  </si>
+  <si>
+    <t>HR &amp; Payroll Specialist</t>
+  </si>
+  <si>
+    <t>The Piedmont Environmental Council</t>
+  </si>
+  <si>
+    <t>Warrenton, VA</t>
+  </si>
+  <si>
+    <t>$25 - $30 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hr--payroll-specialist-warrenton-virginia/4282364153</t>
+  </si>
+  <si>
+    <t>James River Association - Upper James Environmental Educator</t>
+  </si>
+  <si>
+    <t>James River Association</t>
+  </si>
+  <si>
+    <t>Lynchburg, VA</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-james-river-association---upper-james-environmental-educator-lynchburg-virginia/7303306034</t>
+  </si>
+  <si>
+    <t>Landscape Designer</t>
+  </si>
+  <si>
+    <t>Watershed Progressive</t>
+  </si>
+  <si>
+    <t>Mendocino/Sonoma-Based, CA</t>
+  </si>
+  <si>
+    <t>$73,500 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-landscape-designer-sonoma-california/6001452466</t>
+  </si>
+  <si>
+    <t>Licensed Landscape Architect</t>
+  </si>
+  <si>
+    <t>$110,000 - $145,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-licensed-landscape-architect-mendocinosonoma-based-california/1602821360</t>
+  </si>
+  <si>
+    <t>Maintenance Specialis Individual Placement</t>
+  </si>
+  <si>
+    <t>Conservation Corps New Mexico</t>
+  </si>
+  <si>
+    <t>San Acacia, NM</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$765 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-maintenance-specialis-individual-placement-san-acacia-new-mexico/6450723832</t>
+  </si>
+  <si>
+    <t>Medical Care Internship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-medical-care-internship-south-padre-island-texas/8341333386</t>
+  </si>
+  <si>
+    <t>Nature's Classroom Instructor</t>
+  </si>
+  <si>
+    <t>Ohio FFA Camp Muskingum</t>
+  </si>
+  <si>
+    <t>Carrollton, OH</t>
+  </si>
+  <si>
+    <t>$485 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natures-classroom-instructor-carrollton-ohio/5928090068</t>
+  </si>
+  <si>
+    <t>Network Coordinator</t>
+  </si>
+  <si>
+    <t>Northeast Wilderness Trust</t>
+  </si>
+  <si>
+    <t>Montpelier, VT</t>
+  </si>
+  <si>
+    <t>$42 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-network-coordinator-montpelier-vermont/7966025066</t>
+  </si>
+  <si>
+    <t>Outdoor Logistics Coordinator</t>
+  </si>
+  <si>
+    <t>Pisgah Forest, NC</t>
+  </si>
+  <si>
+    <t>$400 - $455 per week</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-logistics-coordinator-pisgah-forest-north-carolina/2600559767</t>
+  </si>
+  <si>
+    <t>Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Laguna Canyon Foundation</t>
+  </si>
+  <si>
+    <t>Laguna Beach, CA</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outreach-coordinator-laguna-beach-california/6332566202</t>
+  </si>
+  <si>
+    <t>Paid AmeriCorps Volunteer</t>
+  </si>
+  <si>
+    <t>AmeriCorps READY</t>
+  </si>
+  <si>
+    <t>Detroit, MI</t>
+  </si>
+  <si>
+    <t>$12 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-paid-americorps-volunteer-detroit-michigan/1442726485</t>
+  </si>
+  <si>
+    <t>Permit Writer (Environmental Specialist 4)</t>
+  </si>
+  <si>
+    <t>WA State Department of Ecology</t>
+  </si>
+  <si>
+    <t>Lacey, WA</t>
+  </si>
+  <si>
+    <t>$69,348 - $93,288 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-permit-writer-environmental-specialist-4-lacey-washington/7753538999</t>
+  </si>
+  <si>
+    <t>Project Based Wetland Scientist</t>
+  </si>
+  <si>
+    <t>Midwest Wetland Improvements</t>
+  </si>
+  <si>
+    <t>Victoria, MN</t>
+  </si>
+  <si>
+    <t>$30 - $45 per hour</t>
+  </si>
+  <si>
+    <t>botany-ecology-general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-project-based-wetland-scientist-victoria-minnesota/3854237577</t>
+  </si>
+  <si>
+    <t>Property Management Specialist I/II</t>
+  </si>
+  <si>
+    <t>Midpeninsula Regional Open Space District</t>
+  </si>
+  <si>
+    <t>Los Altos, CA</t>
+  </si>
+  <si>
+    <t>$104,411 - $143,735 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-property-management-specialist-iii-los-altos-ca-california/8219995988</t>
+  </si>
+  <si>
+    <t>Public Lands Defense Fellow</t>
+  </si>
+  <si>
+    <t>Friends of the Inyo</t>
+  </si>
+  <si>
+    <t>Bishop, CA</t>
+  </si>
+  <si>
+    <t>$23 - $26 per hour</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-lands-defense-fellow-bishop-california/3728468789</t>
+  </si>
+  <si>
+    <t>Recovery Coordinator</t>
+  </si>
+  <si>
+    <t>Yakima Basin Fish and Wildlife Recovery Board</t>
+  </si>
+  <si>
+    <t>Yakima, WA</t>
+  </si>
+  <si>
+    <t>$65,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>fisheries-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-recovery-coordinator-yakima-washington/6962897060</t>
+  </si>
+  <si>
+    <t>Regional Construction Supervisor</t>
+  </si>
+  <si>
+    <t>Ojai, CA</t>
+  </si>
+  <si>
+    <t>$82,000 - $105,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-construction-supervisor-ojai-california/1229465706</t>
+  </si>
+  <si>
+    <t>Regional Landscape Construction Foreperson</t>
+  </si>
+  <si>
+    <t>Groveland, CA</t>
+  </si>
+  <si>
+    <t>$73,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-landscape-construction-foreperson-groveland-california/1283330949</t>
+  </si>
+  <si>
+    <t>Senior Director, Leadership Giving</t>
+  </si>
+  <si>
+    <t>National Audubon Society</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>$186,000 - $208,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-director-leadership-giving-oakland-california/2661615461</t>
+  </si>
+  <si>
+    <t>Trip Leader</t>
+  </si>
+  <si>
+    <t>$350 - $385 per week</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-trip-leader-pisgah-forest-north-carolina/6812596826</t>
+  </si>
+  <si>
+    <t>Water Resource Field Specialist I/II</t>
+  </si>
+  <si>
+    <t>$25 - $35 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resource-field-specialist-iii-groveland-california/1853417950</t>
+  </si>
+  <si>
+    <t>Wetland and Waterway Permit and Enforcement Coordinator</t>
+  </si>
+  <si>
+    <t>Dept. of State Lands - Oregon</t>
+  </si>
+  <si>
+    <t>Salem, OR</t>
+  </si>
+  <si>
+    <t>$5,320 - $8,141 per month</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wetland-and-waterway-permit-and-enforcement-coordinator-salem-oregon/3097131370</t>
+  </si>
+  <si>
+    <t>Wetland Ecologist</t>
+  </si>
+  <si>
+    <t>Oregon Dept. of State Lands</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wetland-ecologist-salem-oregon/3568333136</t>
+  </si>
+  <si>
+    <t>Wildland Fire Crew Superintendent</t>
+  </si>
+  <si>
+    <t>Stanwood, WA</t>
+  </si>
+  <si>
+    <t>$54,204 - $72,900 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-crew-superintendent-stanwood-wa-washington/8614142530</t>
+  </si>
+  <si>
+    <t>Wildland Fire Hand Crew Foreman</t>
+  </si>
+  <si>
+    <t>Cle Elum, WA</t>
+  </si>
+  <si>
+    <t>$50,412 - $67,704 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-hand-crew-foreman-cle-elum-washington/8856441487</t>
+  </si>
+  <si>
+    <t>Wildland Fire Regulation and Prevention Technician</t>
+  </si>
+  <si>
+    <t>Colville, WA</t>
+  </si>
+  <si>
+    <t>$45,924 - $67,704 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-regulation-and-prevention-technician-colville-washington/9638140632</t>
+  </si>
+  <si>
+    <t>Wildland Fire Squad Boss</t>
+  </si>
+  <si>
+    <t>Bellingham, WA</t>
+  </si>
+  <si>
+    <t>$45,924 - $61,332 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-squad-boss-bellingham-washington/1303252002</t>
+  </si>
+  <si>
+    <t>Wildlife Biologist 2/3</t>
+  </si>
+  <si>
+    <t>Alaska Department of Fish and Game</t>
+  </si>
+  <si>
+    <t>Kotzebue, AK</t>
+  </si>
+  <si>
+    <t>$8,248 - $9,475 per month</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist-23-kotzebue-alaska/3632353033</t>
+  </si>
+  <si>
+    <t>Wildlife Technician</t>
+  </si>
+  <si>
+    <t>Arizona Game and Fish Department</t>
+  </si>
+  <si>
+    <t>Phoenix, AZ</t>
+  </si>
+  <si>
+    <t>$17.45 - $20.19 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-technician-phoenix-arizona/7999626182</t>
+  </si>
+  <si>
+    <t>Land Conservation Manager</t>
+  </si>
+  <si>
+    <t>New Mexico Land Conservancy</t>
+  </si>
+  <si>
+    <t>Santa Fe, New Mexico, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/land-conservation-manager-3/</t>
+  </si>
+  <si>
+    <t>Ability:IMPACT Program Coordinator</t>
+  </si>
+  <si>
+    <t>IMPACT Boston</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Disability, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0bcb29df7bf04417a42681826555f599-abilityimpact-program-coordinator-impact-boston-boston</t>
+  </si>
+  <si>
+    <t>Administrative Assistant to the EVP/Chief Programs &amp; Fellowships Officer</t>
+  </si>
+  <si>
+    <t>C&amp;S</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50a42a449f9740648e862af652029d6b-administrative-assistant-to-the-evpchief-programs-fellowships-officer-cs-princeton</t>
+  </si>
+  <si>
+    <t>Advocacy Director</t>
+  </si>
+  <si>
+    <t>Mental Health Legal Advisors Committee</t>
+  </si>
+  <si>
+    <t>Quincy, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 124245.00 - 183654.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Mental Health, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/f070074202ff444b94a176c9cf07d64a-advocacy-director-mental-health-legal-advisors-committee-quincy</t>
+  </si>
+  <si>
+    <t>Associate Community Organizer</t>
+  </si>
+  <si>
+    <t>Direct Action &amp; Research Training Center</t>
+  </si>
+  <si>
+    <t>Lakeland, Florida</t>
+  </si>
+  <si>
+    <t>USD 52000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a41395dadc14e6d8919852b05396298-associate-community-organizer-direct-action-research-training-center-lakeland</t>
+  </si>
+  <si>
+    <t>Associate Director of Communications</t>
+  </si>
+  <si>
+    <t>Transportation Alternatives</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4078355dd20d44d6901070471cbfb710-associate-director-of-communications-transportation-alternatives-new-york</t>
+  </si>
+  <si>
+    <t>Associate, Conferences and Events</t>
+  </si>
+  <si>
+    <t>Council on Foundations</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 34.33 - 38.37/hour</t>
+  </si>
+  <si>
+    <t>Philanthropy, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ed1f2a277d9430598446c8f3452911b-associate-conferences-and-events-council-on-foundations-washington</t>
+  </si>
+  <si>
+    <t>Bilingual Paralegal - Social Security Income (SSI)</t>
+  </si>
+  <si>
+    <t>Legal Services of New Jersey</t>
+  </si>
+  <si>
+    <t>Edison, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 54000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63a67dec205341df9bbbb0e28dcf347f-bilingual-paralegal-social-security-income-ssi-legal-services-of-new-jersey-edison</t>
+  </si>
+  <si>
+    <t>Building Supervisor</t>
+  </si>
+  <si>
+    <t>Linworth United Methodist Church</t>
+  </si>
+  <si>
+    <t>Columbus, Ohio</t>
+  </si>
+  <si>
+    <t>USD 45760.00 - 49920.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de7467d9b1ef4ab9a3480e2a5ea2701e-building-supervisor-linworth-united-methodist-church-columbus</t>
+  </si>
+  <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>ACE (Association of Community Employment Programs for the Homeless, Inc.)</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Housing Homelessness, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b2d0b5bcf354d599a5403934c42cf27-case-manager-ace-association-of-community-employment-programs-for-the-homeless-inc-queens-county</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>Telluride Association</t>
+  </si>
+  <si>
+    <t>Ithaca, NY</t>
+  </si>
+  <si>
+    <t>USD 90317.00 - 112897.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f9d9dc6f76c94ddda7734e37eae2ea92-chief-financial-officer-telluride-association-ithaca</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>Animal Advocacy Careers</t>
+  </si>
+  <si>
+    <t>Animals, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f02f6d1451784035a1788a0fe5d4ff03-chief-operating-officer-animal-advocacy-careers-london</t>
+  </si>
+  <si>
+    <t>Communications Consultant</t>
+  </si>
+  <si>
+    <t>GreenRoots, Inc.</t>
+  </si>
+  <si>
+    <t>Chelsea, Massachusetts</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87db713c009240dd91c1903698760548-communications-consultant-greenroots-inc-chelsea</t>
+  </si>
+  <si>
+    <t>Community Relations Coordinator</t>
+  </si>
+  <si>
+    <t>Indiana Statewide Independent Living Council</t>
+  </si>
+  <si>
+    <t>Indianapolis, Indiana</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77b5ba00dad64964a4d6a363f78fd167-community-relations-coordinator-indiana-statewide-independent-living-council-indianapolis</t>
+  </si>
+  <si>
+    <t>Contract Enforcement Administrative Assistant #ADM#</t>
+  </si>
+  <si>
+    <t>Hotel and Gaming Trades Council, AFL-CIO</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 29.11 - 29.11/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a4870e59dc374aad9c7bfe096ba305c6-contract-enforcement-administrative-assistant-adm-hotel-and-gaming-trades-council-afl-cio-new-york</t>
+  </si>
+  <si>
+    <t>Cuidadoras/es Sociales para el programa de Córdoba</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS Argentina</t>
+  </si>
+  <si>
+    <t>Córdoba, Córdoba, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/807b054b0d2744f08fb6190815ebd57f-cuidadorases-sociales-para-el-programa-de-cordoba-aldeas-infantiles-sos-argentina-cordoba</t>
+  </si>
+  <si>
+    <t>Cuidadoras/es Sociales para el programa de Luján</t>
+  </si>
+  <si>
+    <t>Luján, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61e81b4738374f5aa8f3d67bc2a86729-cuidadorases-sociales-para-el-programa-de-lujan-aldeas-infantiles-sos-argentina-lujan</t>
+  </si>
+  <si>
+    <t>Cuidadoras/es Sociales para el programa de Oberá</t>
+  </si>
+  <si>
+    <t>Oberá, Misiones, AR</t>
+  </si>
+  <si>
+    <t>Community Development, Family, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/143af854372b49ef85997036fc217448-cuidadorases-sociales-para-el-programa-de-obera-aldeas-infantiles-sos-argentina-obera</t>
+  </si>
+  <si>
+    <t>Data Analyst</t>
+  </si>
+  <si>
+    <t>Unite America</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c82affff8bff42c2885e1f9e08c65cc4-data-analyst-unite-america-denver</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Democracy North Carolina</t>
+  </si>
+  <si>
+    <t>Morrisville, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 93000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26f18f345abc432d96b157f8af4691a0-development-director-democracy-north-carolina-morrisville</t>
+  </si>
+  <si>
+    <t>Digital Marketing &amp; Social Media Specialist</t>
+  </si>
+  <si>
+    <t>Global Culture Network</t>
+  </si>
+  <si>
+    <t>International Relations, Communications Access, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/81156b473f78408c84f814894050e4e9-digital-marketing-social-media-specialist-global-culture-network-abuja</t>
+  </si>
+  <si>
+    <t>Director of Development &amp; Fundraising</t>
+  </si>
+  <si>
+    <t>Conexión Américas</t>
+  </si>
+  <si>
+    <t>Nashville, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 87000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49a6ceb2bd64481aaeaab9ad2173cd5d-director-of-development-fundraising-conexion-americas-nashville</t>
+  </si>
+  <si>
+    <t>Director of Development and Finance</t>
+  </si>
+  <si>
+    <t>Interfaith Philadelphia</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Religion Spirituality, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ad4890c9e924e3fb19e01b40c433da1-director-of-development-and-finance-interfaith-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Director of Research</t>
+  </si>
+  <si>
+    <t>Initiative for a Competitive Inner City (ICIC)</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53402a0191574432ba91c94a73385d28-director-of-research-initiative-for-a-competitive-inner-city-icic-boston</t>
+  </si>
+  <si>
+    <t>Director of Workforce Development</t>
+  </si>
+  <si>
+    <t>St. Francis House</t>
+  </si>
+  <si>
+    <t>USD 106000.00 - 117000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1743550bbf8e4de6b40e1632e4586663-director-of-workforce-development-st-francis-house-boston</t>
+  </si>
+  <si>
+    <t>Director of Youth Ministries</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 19000.00 - 22000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee53b74dd94a4c62a773fd4ccda22cd6-director-of-youth-ministries-linworth-united-methodist-church-columbus</t>
+  </si>
+  <si>
+    <t>Director, Programs</t>
+  </si>
+  <si>
+    <t>Resources for Abortion Delivery</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c807582318084bd7842148940154b1d2-director-programs-resources-for-abortion-delivery-washington</t>
+  </si>
+  <si>
+    <t>Early Childhood Center Office Administrator</t>
+  </si>
+  <si>
+    <t>Bender JCC Early Childhood Center</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d9fea987dc07443992b7a02fc0ad2939-early-childhood-center-office-administrator-bender-jcc-early-childhood-center-rockville</t>
+  </si>
+  <si>
+    <t>Elementary Math Teaching Assistant for After School Club</t>
+  </si>
+  <si>
+    <t>The Art of Problem Solving Initiative, Inc.</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 19.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/524b9a1b186b4457aa6552e570eed427-elementary-math-teaching-assistant-for-after-school-club-the-art-of-problem-solving-initiative-inc-new-york</t>
+  </si>
+  <si>
+    <t>HealthQ</t>
+  </si>
+  <si>
+    <t>Haverhill, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 205000.00 - 205000.00/year</t>
+  </si>
+  <si>
+    <t>Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f7060cc96413483080b5292d445d43b4-executive-director-healthq-haverhill</t>
+  </si>
+  <si>
+    <t>Executive Director, Compost Research &amp; Education Foundation (CREF)</t>
+  </si>
+  <si>
+    <t>Compost Research &amp; Education Foundation</t>
+  </si>
+  <si>
+    <t>Remote (North Carolina)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/543d71d9410d426c99d1df21a2c3a0c6-executive-director-compost-research-education-foundation-cref-compost-research-education-foundation-raleigh</t>
+  </si>
+  <si>
+    <t>Family Intervention Specialist</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Jackson, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bdcced3be7ba43059f0cc3735352c6e8-family-intervention-specialist-youth-villages-jackson</t>
+  </si>
+  <si>
+    <t>Columbia, Tennessee</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3d6e3499e0714377a420efb1c66f43b7-family-intervention-specialist-youth-villages-columbia</t>
+  </si>
+  <si>
+    <t>Family Resource Coordinator - Bilingual Spanish</t>
+  </si>
+  <si>
+    <t>Community Action Partnership for Dutchess County, Inc.</t>
+  </si>
+  <si>
+    <t>Dover Plains, New York</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a3137fdece44fc8be5e2db7b5dfd51a-family-resource-coordinator-bilingual-spanish-community-action-partnership-for-dutchess-county-inc-dover-plains</t>
+  </si>
+  <si>
+    <t>Family Service Worker</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ecb4ad1454194174823923786576fd07-family-service-worker-youth-villages-nashville</t>
+  </si>
+  <si>
+    <t>Full-time Program Director</t>
+  </si>
+  <si>
+    <t>Columbia County Community Healthcare Consortium, Inc.</t>
+  </si>
+  <si>
+    <t>Hudson, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 69000.00/year</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b9e4e8ba88b4cc297311a7da6590f1c-full-time-program-director-columbia-county-community-healthcare-consortium-inc-hudson</t>
+  </si>
+  <si>
+    <t>Grant Writer</t>
+  </si>
+  <si>
+    <t>Friends of the Stone Church @ The Stone Church Cultural Center</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/872279cba7bf43708029af8edb93feee-grant-writer-friends-of-the-stone-church-the-stone-church-cultural-center-gilbertville</t>
+  </si>
+  <si>
+    <t>Housing Staff Attorney</t>
+  </si>
+  <si>
+    <t>Safety Net Project - Urban Justice Center</t>
+  </si>
+  <si>
+    <t>USD 78433.00 - 103819.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b309a637f8b3485b8ec48b6864be67c0-housing-staff-attorney-safety-net-project-urban-justice-center-new-york</t>
+  </si>
+  <si>
+    <t>HR Manager</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/5b5e03eaed234d0b80b852ec3e31a9b2-hr-manager-global-culture-network-abuja</t>
+  </si>
+  <si>
+    <t>JOIN A PROGRESSIVE CAMPAIGN IN CALIFORNIA’S 48TH CONGRESSIONAL DISTRICT!</t>
+  </si>
+  <si>
+    <t>Worker Power</t>
+  </si>
+  <si>
+    <t>Murrieta, California</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 23.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/604688e58bb54e73b543581ed409e26a-join-a-progressive-campaign-in-californias-48th-congressional-district-worker-power-murrieta</t>
+  </si>
+  <si>
+    <t>Legal Advocate</t>
+  </si>
+  <si>
+    <t>USD 80581.54 - 120555.76/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/073891c249e7419a9754aac6e24387cf-legal-advocate-mental-health-legal-advisors-committee-quincy</t>
+  </si>
+  <si>
+    <t>Legal Manager</t>
+  </si>
+  <si>
+    <t>Justice in Motion</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 84750.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9883443955d348e3a0ad5749ff8e8f0f-legal-manager-justice-in-motion-brooklyn</t>
+  </si>
+  <si>
+    <t>Loan and Business Development Officer</t>
+  </si>
+  <si>
+    <t>The Housing Partnership Network</t>
+  </si>
+  <si>
+    <t>Tulsa, Oklahoma</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e49381dc4a5a41faaffc715b7aaa684f-loan-and-business-development-officer-the-housing-partnership-network-tulsa</t>
+  </si>
+  <si>
+    <t>Manager, Human Resources Partnerships</t>
+  </si>
+  <si>
+    <t>Earthjustice</t>
+  </si>
+  <si>
+    <t>USD 155700.00 - 203500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4c7ff04fbcb640b6bf706a515301ca4a-manager-human-resources-partnerships-earthjustice-washington</t>
+  </si>
+  <si>
+    <t>Manager, Marketing, Communications and External Affairs</t>
+  </si>
+  <si>
+    <t>Jewish Community Council of Greater Coney Island</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d7d95e12971c468ca55bd231714a0a0d-manager-marketing-communications-and-external-affairs-jewish-community-council-of-greater-coney-island-kings-county</t>
+  </si>
+  <si>
+    <t>Manager, Messaging Strategy</t>
+  </si>
+  <si>
+    <t>Sightline Institute</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0d736dca60c40f5b09fe1610bfd182c-manager-messaging-strategy-sightline-institute-seattle</t>
+  </si>
+  <si>
+    <t>Managing Director of Institutional Fundraising</t>
+  </si>
+  <si>
+    <t>KID smART</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f8a5911b49e40fbad560652c034abf6-managing-director-of-institutional-fundraising-kid-smart-new-orleans</t>
+  </si>
+  <si>
+    <t>Marketing Project Manager (Campus &amp; Experiences)</t>
+  </si>
+  <si>
+    <t>National Geographic Society</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 80750.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/563c82a4a5404dcaad796c6d93844e40-marketing-project-manager-campus-experiences-national-geographic-society-washington</t>
+  </si>
+  <si>
+    <t>NY Renews Coalition Organizer</t>
+  </si>
+  <si>
+    <t>NY Renews</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f1c40626f694ae3af48a957b155650e-ny-renews-coalition-organizer-ny-renews-new-york</t>
+  </si>
+  <si>
+    <t>Office Administrator</t>
+  </si>
+  <si>
+    <t>Christ Episcopal Church, Needham, MA</t>
+  </si>
+  <si>
+    <t>Needham, MA</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dda96bbb1129458f91edd00499a3bfcf-office-administrator-christ-episcopal-church-needham-ma-needham</t>
+  </si>
+  <si>
+    <t>Officer, State Decarbonization Campaign Lead</t>
+  </si>
+  <si>
+    <t>Pew Charitable Trusts</t>
+  </si>
+  <si>
+    <t>USD 121100.00 - 135400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/52d5e073b0a24c40a1582a7813275ae5-officer-state-decarbonization-campaign-lead-pew-charitable-trusts-washington</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Mid Ohio Market</t>
+  </si>
+  <si>
+    <t>Reynoldsburg, Ohio</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 57500.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/00e76af545dc460480e3fcc71e8cdfd9-operations-manager-mid-ohio-market-reynoldsburg</t>
+  </si>
+  <si>
+    <t>Part-time Assistant Resident Manager</t>
+  </si>
+  <si>
+    <t>Love Life Women's Sober Living</t>
+  </si>
+  <si>
+    <t>Steamboat Springs, Colorado</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Mental Health, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/443a84f49eac4246a3b14eca7e9d0381-part-time-assistant-resident-manager-love-life-womens-sober-living-steamboat-springs</t>
+  </si>
+  <si>
+    <t>Partner, External Relations</t>
+  </si>
+  <si>
+    <t>Education Forward DC</t>
+  </si>
+  <si>
+    <t>USD 215378.00 - 215378.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a960c1ca1e364aa18a3b870a4b842a60-partner-external-relations-education-forward-dc-washington</t>
+  </si>
+  <si>
+    <t>Philanthropy Operations Manager</t>
+  </si>
+  <si>
+    <t>Covenant House Michigan</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61592af416b84c9bb2facc0deb20734c-philanthropy-operations-manager-covenant-house-michigan-detroit</t>
+  </si>
+  <si>
+    <t>Prestador/a de Servicios de Mantenimiento</t>
+  </si>
+  <si>
+    <t>Mar del Plata, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9368a1529c8e46f990697ff4c21287f0-prestadora-de-servicios-de-mantenimiento-aldeas-infantiles-sos-argentina-mar-del-plata</t>
+  </si>
+  <si>
+    <t>Program Associate, Youth Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee7f13e4e72b4d26b6e1261e146a1d20-program-associate-youth-engagement-cs-princeton</t>
+  </si>
+  <si>
+    <t>Program Director, Feeding Our Neighbors (FON)</t>
+  </si>
+  <si>
+    <t>Catholic Charities Archdiocese of NY</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1c1578a97614cb1b02ad64fb29648df-program-director-feeding-our-neighbors-fon-catholic-charities-archdiocese-of-ny-bronx-county</t>
+  </si>
+  <si>
+    <t>Program Officer, Social Impact</t>
+  </si>
+  <si>
+    <t>Panorama Global</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80d9627e464a493bae29a8b7f3e2ab1d-program-officer-social-impact-panorama-global-new-york</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e66b6e02fe64f349e339ebaeb1b7fc8-program-officer-social-impact-panorama-global-seattle</t>
+  </si>
+  <si>
+    <t>School Based Advisor</t>
+  </si>
+  <si>
+    <t>College Success Foundation</t>
+  </si>
+  <si>
+    <t>Tacoma, Washington</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 34.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afa5f2d111e24bf9976d825d37807f25-school-based-advisor-college-success-foundation-tacoma</t>
+  </si>
+  <si>
+    <t>Senior Client Services Coordinator</t>
+  </si>
+  <si>
+    <t>Shine Foundation Inc</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f297198730e0490e9e4a6109602b1250-senior-client-services-coordinator-shine-foundation-inc-new-york</t>
+  </si>
+  <si>
+    <t>Senior Coordinator, Data Operations</t>
+  </si>
+  <si>
+    <t>Travis Manion Foundation</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8c5fcc1435f4518a9d2c30c179369b7-senior-coordinator-data-operations-travis-manion-foundation-doylestown</t>
+  </si>
+  <si>
+    <t>Senior Manager, Digital Fundraising</t>
+  </si>
+  <si>
+    <t>USD 106400.00 - 112000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c9aa6cee3e9546818a40f82030f9f152-senior-manager-digital-fundraising-national-geographic-society-washington</t>
+  </si>
+  <si>
+    <t>Senior Media Relations Specialist</t>
+  </si>
+  <si>
+    <t>Hadassah, WZOA, Inc.</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de4d5fe14d2d4fd1baf74b98521439cd-senior-media-relations-specialist-hadassah-wzoa-inc-new-york</t>
+  </si>
+  <si>
+    <t>Senior Specialist, Operations</t>
+  </si>
+  <si>
+    <t>Chef Ann Foundation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0d3036187fd442a3b20df56add314451-senior-specialist-operations-chef-ann-foundation-boulder</t>
+  </si>
+  <si>
+    <t>Specialist, Operations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/01171c14d95c4452b2690381e6aba40a-specialist-operations-chef-ann-foundation-boulder</t>
+  </si>
+  <si>
+    <t>State Organizer for Texas (Hunger and Poverty Advocacy)</t>
+  </si>
+  <si>
+    <t>Bread for the World, Inc.</t>
+  </si>
+  <si>
+    <t>Remote (Texas)</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Poverty, Religion Spirituality, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e8eb533799446c19a2fa69e3fae8903-state-organizer-for-texas-hunger-and-poverty-advocacy-bread-for-the-world-inc-houston</t>
+  </si>
+  <si>
+    <t>The Pauli Murray Fellowship, Communications Team</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96d807c453324f2d8e34bfc8cf12210b-the-pauli-murray-fellowship-communications-team-american-civil-liberties-union-new-york</t>
+  </si>
+  <si>
+    <t>The Pauli Murray Fellowship, EDIB Team</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7a7ab571c944abcb7eb57845afa2ee1-the-pauli-murray-fellowship-edib-team-american-civil-liberties-union-new-york</t>
+  </si>
+  <si>
+    <t>Therapist - Adolescent Health Center</t>
+  </si>
+  <si>
+    <t>The Door - A Center of Alternatives</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f8bb5811b9a4ec7bb1ba8e08e2681b3-therapist-adolescent-health-center-the-door-a-center-of-alternatives-new-york</t>
+  </si>
+  <si>
+    <t>Vice President, Distribution &amp; New Revenue</t>
+  </si>
+  <si>
+    <t>The WNET Group</t>
+  </si>
+  <si>
+    <t>USD 277000.00 - 297000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10581785d9ac4e46b01a1e51992ec3a2-vice-president-distribution-new-revenue-the-wnet-group-new-york</t>
+  </si>
+  <si>
+    <t>Warehouse Supervisor</t>
+  </si>
+  <si>
+    <t>Small Things, Inc.</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f625664f1243419988e9e7653f34ea57-warehouse-supervisor-small-things-inc-philadelphia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1794,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1820,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2202,1018 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>121</v>
+      </c>
+      <c r="F23" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F24" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" t="s">
+        <v>134</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27" t="s">
+        <v>146</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" t="s">
+        <v>152</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" t="s">
+        <v>164</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" t="s">
+        <v>128</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" t="s">
+        <v>181</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>183</v>
+      </c>
+      <c r="B35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
+        <v>184</v>
+      </c>
+      <c r="F35" t="s">
+        <v>185</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" t="s">
+        <v>188</v>
+      </c>
+      <c r="C36" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" t="s">
+        <v>190</v>
+      </c>
+      <c r="F36" t="s">
+        <v>191</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
+        <v>190</v>
+      </c>
+      <c r="F37" t="s">
+        <v>191</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>198</v>
+      </c>
+      <c r="F38" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>201</v>
+      </c>
+      <c r="B39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" t="s">
+        <v>202</v>
+      </c>
+      <c r="D39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>203</v>
+      </c>
+      <c r="F39" t="s">
+        <v>199</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>207</v>
+      </c>
+      <c r="F40" t="s">
+        <v>199</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>209</v>
+      </c>
+      <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="s">
+        <v>210</v>
+      </c>
+      <c r="D41" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" t="s">
+        <v>211</v>
+      </c>
+      <c r="F41" t="s">
+        <v>199</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>213</v>
+      </c>
+      <c r="B42" t="s">
+        <v>214</v>
+      </c>
+      <c r="C42" t="s">
+        <v>215</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" t="s">
+        <v>216</v>
+      </c>
+      <c r="F42" t="s">
+        <v>217</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" t="s">
+        <v>220</v>
+      </c>
+      <c r="C43" t="s">
+        <v>221</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>222</v>
+      </c>
+      <c r="F43" t="s">
+        <v>217</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -466,7 +3221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -505,8 +3260,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3295,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3334,1738 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F3" t="s">
+        <v>242</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F4" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D6" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F6" t="s">
+        <v>260</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F7" t="s">
+        <v>266</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" t="s">
+        <v>234</v>
+      </c>
+      <c r="E8" t="s">
+        <v>271</v>
+      </c>
+      <c r="F8" t="s">
+        <v>272</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F9" t="s">
+        <v>278</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D10" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F10" t="s">
+        <v>284</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D11" t="s">
+        <v>234</v>
+      </c>
+      <c r="E11" t="s">
+        <v>289</v>
+      </c>
+      <c r="F11" t="s">
+        <v>290</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F12" t="s">
+        <v>294</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>296</v>
+      </c>
+      <c r="B13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" t="s">
+        <v>298</v>
+      </c>
+      <c r="D13" t="s">
+        <v>299</v>
+      </c>
+      <c r="E13" t="s">
+        <v>300</v>
+      </c>
+      <c r="F13" t="s">
+        <v>301</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14" t="s">
+        <v>304</v>
+      </c>
+      <c r="C14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D14" t="s">
+        <v>234</v>
+      </c>
+      <c r="E14" t="s">
+        <v>306</v>
+      </c>
+      <c r="F14" t="s">
+        <v>307</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" t="s">
+        <v>310</v>
+      </c>
+      <c r="C15" t="s">
+        <v>311</v>
+      </c>
+      <c r="D15" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" t="s">
+        <v>312</v>
+      </c>
+      <c r="F15" t="s">
+        <v>313</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>315</v>
+      </c>
+      <c r="B16" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" t="s">
+        <v>317</v>
+      </c>
+      <c r="D16" t="s">
+        <v>234</v>
+      </c>
+      <c r="E16" t="s">
+        <v>228</v>
+      </c>
+      <c r="F16" t="s">
+        <v>318</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>320</v>
+      </c>
+      <c r="B17" t="s">
+        <v>316</v>
+      </c>
+      <c r="C17" t="s">
+        <v>321</v>
+      </c>
+      <c r="D17" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" t="s">
+        <v>228</v>
+      </c>
+      <c r="F17" t="s">
+        <v>322</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B18" t="s">
+        <v>316</v>
+      </c>
+      <c r="C18" t="s">
+        <v>325</v>
+      </c>
+      <c r="D18" t="s">
+        <v>234</v>
+      </c>
+      <c r="E18" t="s">
+        <v>228</v>
+      </c>
+      <c r="F18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>328</v>
+      </c>
+      <c r="B19" t="s">
+        <v>329</v>
+      </c>
+      <c r="C19" t="s">
+        <v>330</v>
+      </c>
+      <c r="D19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E19" t="s">
+        <v>331</v>
+      </c>
+      <c r="F19" t="s">
+        <v>332</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>334</v>
+      </c>
+      <c r="B20" t="s">
+        <v>335</v>
+      </c>
+      <c r="C20" t="s">
+        <v>336</v>
+      </c>
+      <c r="D20" t="s">
+        <v>234</v>
+      </c>
+      <c r="E20" t="s">
+        <v>337</v>
+      </c>
+      <c r="F20" t="s">
+        <v>338</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>340</v>
+      </c>
+      <c r="B21" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" t="s">
+        <v>240</v>
+      </c>
+      <c r="D21" t="s">
+        <v>234</v>
+      </c>
+      <c r="E21" t="s">
+        <v>228</v>
+      </c>
+      <c r="F21" t="s">
+        <v>342</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>344</v>
+      </c>
+      <c r="B22" t="s">
+        <v>345</v>
+      </c>
+      <c r="C22" t="s">
+        <v>346</v>
+      </c>
+      <c r="D22" t="s">
+        <v>234</v>
+      </c>
+      <c r="E22" t="s">
+        <v>347</v>
+      </c>
+      <c r="F22" t="s">
+        <v>228</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>349</v>
+      </c>
+      <c r="B23" t="s">
+        <v>350</v>
+      </c>
+      <c r="C23" t="s">
+        <v>351</v>
+      </c>
+      <c r="D23" t="s">
+        <v>234</v>
+      </c>
+      <c r="E23" t="s">
+        <v>352</v>
+      </c>
+      <c r="F23" t="s">
+        <v>353</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>355</v>
+      </c>
+      <c r="B24" t="s">
+        <v>356</v>
+      </c>
+      <c r="C24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D24" t="s">
+        <v>234</v>
+      </c>
+      <c r="E24" t="s">
+        <v>357</v>
+      </c>
+      <c r="F24" t="s">
+        <v>358</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>360</v>
+      </c>
+      <c r="B25" t="s">
+        <v>361</v>
+      </c>
+      <c r="C25" t="s">
+        <v>233</v>
+      </c>
+      <c r="D25" t="s">
+        <v>234</v>
+      </c>
+      <c r="E25" t="s">
+        <v>362</v>
+      </c>
+      <c r="F25" t="s">
+        <v>363</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>365</v>
+      </c>
+      <c r="B26" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26" t="s">
+        <v>276</v>
+      </c>
+      <c r="D26" t="s">
+        <v>366</v>
+      </c>
+      <c r="E26" t="s">
+        <v>367</v>
+      </c>
+      <c r="F26" t="s">
+        <v>278</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>369</v>
+      </c>
+      <c r="B27" t="s">
+        <v>370</v>
+      </c>
+      <c r="C27" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" t="s">
+        <v>234</v>
+      </c>
+      <c r="E27" t="s">
+        <v>371</v>
+      </c>
+      <c r="F27" t="s">
+        <v>228</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>373</v>
+      </c>
+      <c r="B28" t="s">
+        <v>374</v>
+      </c>
+      <c r="C28" t="s">
+        <v>375</v>
+      </c>
+      <c r="D28" t="s">
+        <v>234</v>
+      </c>
+      <c r="E28" t="s">
+        <v>376</v>
+      </c>
+      <c r="F28" t="s">
+        <v>377</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>379</v>
+      </c>
+      <c r="B29" t="s">
+        <v>380</v>
+      </c>
+      <c r="C29" t="s">
+        <v>311</v>
+      </c>
+      <c r="D29" t="s">
+        <v>366</v>
+      </c>
+      <c r="E29" t="s">
+        <v>381</v>
+      </c>
+      <c r="F29" t="s">
+        <v>382</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C30" t="s">
+        <v>385</v>
+      </c>
+      <c r="D30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E30" t="s">
+        <v>386</v>
+      </c>
+      <c r="F30" t="s">
+        <v>387</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>389</v>
+      </c>
+      <c r="B31" t="s">
+        <v>390</v>
+      </c>
+      <c r="C31" t="s">
+        <v>391</v>
+      </c>
+      <c r="D31" t="s">
+        <v>234</v>
+      </c>
+      <c r="E31" t="s">
+        <v>392</v>
+      </c>
+      <c r="F31" t="s">
+        <v>393</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B32" t="s">
+        <v>396</v>
+      </c>
+      <c r="C32" t="s">
+        <v>397</v>
+      </c>
+      <c r="D32" t="s">
+        <v>234</v>
+      </c>
+      <c r="E32" t="s">
+        <v>398</v>
+      </c>
+      <c r="F32" t="s">
+        <v>399</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>395</v>
+      </c>
+      <c r="B33" t="s">
+        <v>396</v>
+      </c>
+      <c r="C33" t="s">
+        <v>401</v>
+      </c>
+      <c r="D33" t="s">
+        <v>234</v>
+      </c>
+      <c r="E33" t="s">
+        <v>398</v>
+      </c>
+      <c r="F33" t="s">
+        <v>399</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>403</v>
+      </c>
+      <c r="B34" t="s">
+        <v>404</v>
+      </c>
+      <c r="C34" t="s">
+        <v>405</v>
+      </c>
+      <c r="D34" t="s">
+        <v>234</v>
+      </c>
+      <c r="E34" t="s">
+        <v>406</v>
+      </c>
+      <c r="F34" t="s">
+        <v>407</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>409</v>
+      </c>
+      <c r="B35" t="s">
+        <v>396</v>
+      </c>
+      <c r="C35" t="s">
+        <v>346</v>
+      </c>
+      <c r="D35" t="s">
+        <v>234</v>
+      </c>
+      <c r="E35" t="s">
+        <v>398</v>
+      </c>
+      <c r="F35" t="s">
+        <v>399</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>411</v>
+      </c>
+      <c r="B36" t="s">
+        <v>412</v>
+      </c>
+      <c r="C36" t="s">
+        <v>413</v>
+      </c>
+      <c r="D36" t="s">
+        <v>234</v>
+      </c>
+      <c r="E36" t="s">
+        <v>414</v>
+      </c>
+      <c r="F36" t="s">
+        <v>415</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>417</v>
+      </c>
+      <c r="B37" t="s">
+        <v>418</v>
+      </c>
+      <c r="C37" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" t="s">
+        <v>299</v>
+      </c>
+      <c r="E37" t="s">
+        <v>228</v>
+      </c>
+      <c r="F37" t="s">
+        <v>419</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>421</v>
+      </c>
+      <c r="B38" t="s">
+        <v>422</v>
+      </c>
+      <c r="C38" t="s">
+        <v>311</v>
+      </c>
+      <c r="D38" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" t="s">
+        <v>423</v>
+      </c>
+      <c r="F38" t="s">
+        <v>424</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>426</v>
+      </c>
+      <c r="B39" t="s">
+        <v>341</v>
+      </c>
+      <c r="C39" t="s">
+        <v>240</v>
+      </c>
+      <c r="D39" t="s">
+        <v>234</v>
+      </c>
+      <c r="E39" t="s">
+        <v>228</v>
+      </c>
+      <c r="F39" t="s">
+        <v>427</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>429</v>
+      </c>
+      <c r="B40" t="s">
+        <v>430</v>
+      </c>
+      <c r="C40" t="s">
+        <v>431</v>
+      </c>
+      <c r="D40" t="s">
+        <v>432</v>
+      </c>
+      <c r="E40" t="s">
+        <v>433</v>
+      </c>
+      <c r="F40" t="s">
+        <v>434</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>436</v>
+      </c>
+      <c r="B41" t="s">
+        <v>245</v>
+      </c>
+      <c r="C41" t="s">
+        <v>246</v>
+      </c>
+      <c r="D41" t="s">
+        <v>234</v>
+      </c>
+      <c r="E41" t="s">
+        <v>437</v>
+      </c>
+      <c r="F41" t="s">
+        <v>248</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>439</v>
+      </c>
+      <c r="B42" t="s">
+        <v>440</v>
+      </c>
+      <c r="C42" t="s">
+        <v>240</v>
+      </c>
+      <c r="D42" t="s">
+        <v>234</v>
+      </c>
+      <c r="E42" t="s">
+        <v>441</v>
+      </c>
+      <c r="F42" t="s">
+        <v>442</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>444</v>
+      </c>
+      <c r="B43" t="s">
+        <v>445</v>
+      </c>
+      <c r="C43" t="s">
+        <v>446</v>
+      </c>
+      <c r="D43" t="s">
+        <v>234</v>
+      </c>
+      <c r="E43" t="s">
+        <v>228</v>
+      </c>
+      <c r="F43" t="s">
+        <v>447</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>449</v>
+      </c>
+      <c r="B44" t="s">
+        <v>450</v>
+      </c>
+      <c r="C44" t="s">
+        <v>264</v>
+      </c>
+      <c r="D44" t="s">
+        <v>234</v>
+      </c>
+      <c r="E44" t="s">
+        <v>451</v>
+      </c>
+      <c r="F44" t="s">
+        <v>228</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>453</v>
+      </c>
+      <c r="B45" t="s">
+        <v>454</v>
+      </c>
+      <c r="C45" t="s">
+        <v>455</v>
+      </c>
+      <c r="D45" t="s">
+        <v>234</v>
+      </c>
+      <c r="E45" t="s">
+        <v>456</v>
+      </c>
+      <c r="F45" t="s">
+        <v>457</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>459</v>
+      </c>
+      <c r="B46" t="s">
+        <v>460</v>
+      </c>
+      <c r="C46" t="s">
+        <v>461</v>
+      </c>
+      <c r="D46" t="s">
+        <v>234</v>
+      </c>
+      <c r="E46" t="s">
+        <v>462</v>
+      </c>
+      <c r="F46" t="s">
+        <v>463</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>465</v>
+      </c>
+      <c r="B47" t="s">
+        <v>466</v>
+      </c>
+      <c r="C47" t="s">
+        <v>467</v>
+      </c>
+      <c r="D47" t="s">
+        <v>234</v>
+      </c>
+      <c r="E47" t="s">
+        <v>468</v>
+      </c>
+      <c r="F47" t="s">
+        <v>469</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>471</v>
+      </c>
+      <c r="B48" t="s">
+        <v>472</v>
+      </c>
+      <c r="C48" t="s">
+        <v>473</v>
+      </c>
+      <c r="D48" t="s">
+        <v>234</v>
+      </c>
+      <c r="E48" t="s">
+        <v>474</v>
+      </c>
+      <c r="F48" t="s">
+        <v>475</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>477</v>
+      </c>
+      <c r="B49" t="s">
+        <v>478</v>
+      </c>
+      <c r="C49" t="s">
+        <v>258</v>
+      </c>
+      <c r="D49" t="s">
+        <v>234</v>
+      </c>
+      <c r="E49" t="s">
+        <v>456</v>
+      </c>
+      <c r="F49" t="s">
+        <v>479</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>481</v>
+      </c>
+      <c r="B50" t="s">
+        <v>482</v>
+      </c>
+      <c r="C50" t="s">
+        <v>483</v>
+      </c>
+      <c r="D50" t="s">
+        <v>366</v>
+      </c>
+      <c r="E50" t="s">
+        <v>484</v>
+      </c>
+      <c r="F50" t="s">
+        <v>485</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>487</v>
+      </c>
+      <c r="B51" t="s">
+        <v>488</v>
+      </c>
+      <c r="C51" t="s">
+        <v>264</v>
+      </c>
+      <c r="D51" t="s">
+        <v>234</v>
+      </c>
+      <c r="E51" t="s">
+        <v>489</v>
+      </c>
+      <c r="F51" t="s">
+        <v>228</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>491</v>
+      </c>
+      <c r="B52" t="s">
+        <v>492</v>
+      </c>
+      <c r="C52" t="s">
+        <v>493</v>
+      </c>
+      <c r="D52" t="s">
+        <v>234</v>
+      </c>
+      <c r="E52" t="s">
+        <v>494</v>
+      </c>
+      <c r="F52" t="s">
+        <v>495</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>497</v>
+      </c>
+      <c r="B53" t="s">
+        <v>498</v>
+      </c>
+      <c r="C53" t="s">
+        <v>499</v>
+      </c>
+      <c r="D53" t="s">
+        <v>366</v>
+      </c>
+      <c r="E53" t="s">
+        <v>500</v>
+      </c>
+      <c r="F53" t="s">
+        <v>501</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>503</v>
+      </c>
+      <c r="B54" t="s">
+        <v>504</v>
+      </c>
+      <c r="C54" t="s">
+        <v>264</v>
+      </c>
+      <c r="D54" t="s">
+        <v>234</v>
+      </c>
+      <c r="E54" t="s">
+        <v>505</v>
+      </c>
+      <c r="F54" t="s">
+        <v>506</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>508</v>
+      </c>
+      <c r="B55" t="s">
+        <v>509</v>
+      </c>
+      <c r="C55" t="s">
+        <v>510</v>
+      </c>
+      <c r="D55" t="s">
+        <v>234</v>
+      </c>
+      <c r="E55" t="s">
+        <v>511</v>
+      </c>
+      <c r="F55" t="s">
+        <v>512</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>514</v>
+      </c>
+      <c r="B56" t="s">
+        <v>316</v>
+      </c>
+      <c r="C56" t="s">
+        <v>515</v>
+      </c>
+      <c r="D56" t="s">
+        <v>299</v>
+      </c>
+      <c r="E56" t="s">
+        <v>228</v>
+      </c>
+      <c r="F56" t="s">
+        <v>516</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>518</v>
+      </c>
+      <c r="B57" t="s">
+        <v>239</v>
+      </c>
+      <c r="C57" t="s">
+        <v>240</v>
+      </c>
+      <c r="D57" t="s">
+        <v>234</v>
+      </c>
+      <c r="E57" t="s">
+        <v>352</v>
+      </c>
+      <c r="F57" t="s">
+        <v>242</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>520</v>
+      </c>
+      <c r="B58" t="s">
+        <v>521</v>
+      </c>
+      <c r="C58" t="s">
+        <v>522</v>
+      </c>
+      <c r="D58" t="s">
+        <v>234</v>
+      </c>
+      <c r="E58" t="s">
+        <v>523</v>
+      </c>
+      <c r="F58" t="s">
+        <v>495</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>525</v>
+      </c>
+      <c r="B59" t="s">
+        <v>526</v>
+      </c>
+      <c r="C59" t="s">
+        <v>311</v>
+      </c>
+      <c r="D59" t="s">
+        <v>234</v>
+      </c>
+      <c r="E59" t="s">
+        <v>527</v>
+      </c>
+      <c r="F59" t="s">
+        <v>228</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>525</v>
+      </c>
+      <c r="B60" t="s">
+        <v>526</v>
+      </c>
+      <c r="C60" t="s">
+        <v>529</v>
+      </c>
+      <c r="D60" t="s">
+        <v>234</v>
+      </c>
+      <c r="E60" t="s">
+        <v>527</v>
+      </c>
+      <c r="F60" t="s">
+        <v>228</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>531</v>
+      </c>
+      <c r="B61" t="s">
+        <v>532</v>
+      </c>
+      <c r="C61" t="s">
+        <v>533</v>
+      </c>
+      <c r="D61" t="s">
+        <v>234</v>
+      </c>
+      <c r="E61" t="s">
+        <v>534</v>
+      </c>
+      <c r="F61" t="s">
+        <v>506</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>536</v>
+      </c>
+      <c r="B62" t="s">
+        <v>537</v>
+      </c>
+      <c r="C62" t="s">
+        <v>311</v>
+      </c>
+      <c r="D62" t="s">
+        <v>234</v>
+      </c>
+      <c r="E62" t="s">
+        <v>538</v>
+      </c>
+      <c r="F62" t="s">
+        <v>539</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>541</v>
+      </c>
+      <c r="B63" t="s">
+        <v>542</v>
+      </c>
+      <c r="C63" t="s">
+        <v>240</v>
+      </c>
+      <c r="D63" t="s">
+        <v>234</v>
+      </c>
+      <c r="E63" t="s">
+        <v>543</v>
+      </c>
+      <c r="F63" t="s">
+        <v>544</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>546</v>
+      </c>
+      <c r="B64" t="s">
+        <v>472</v>
+      </c>
+      <c r="C64" t="s">
+        <v>473</v>
+      </c>
+      <c r="D64" t="s">
+        <v>234</v>
+      </c>
+      <c r="E64" t="s">
+        <v>547</v>
+      </c>
+      <c r="F64" t="s">
+        <v>475</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>549</v>
+      </c>
+      <c r="B65" t="s">
+        <v>550</v>
+      </c>
+      <c r="C65" t="s">
+        <v>311</v>
+      </c>
+      <c r="D65" t="s">
+        <v>234</v>
+      </c>
+      <c r="E65" t="s">
+        <v>551</v>
+      </c>
+      <c r="F65" t="s">
+        <v>552</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>554</v>
+      </c>
+      <c r="B66" t="s">
+        <v>555</v>
+      </c>
+      <c r="C66" t="s">
+        <v>240</v>
+      </c>
+      <c r="D66" t="s">
+        <v>234</v>
+      </c>
+      <c r="E66" t="s">
+        <v>228</v>
+      </c>
+      <c r="F66" t="s">
+        <v>228</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>557</v>
+      </c>
+      <c r="B67" t="s">
+        <v>555</v>
+      </c>
+      <c r="C67" t="s">
+        <v>240</v>
+      </c>
+      <c r="D67" t="s">
+        <v>234</v>
+      </c>
+      <c r="E67" t="s">
+        <v>228</v>
+      </c>
+      <c r="F67" t="s">
+        <v>228</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>559</v>
+      </c>
+      <c r="B68" t="s">
+        <v>560</v>
+      </c>
+      <c r="C68" t="s">
+        <v>561</v>
+      </c>
+      <c r="D68" t="s">
+        <v>234</v>
+      </c>
+      <c r="E68" t="s">
+        <v>562</v>
+      </c>
+      <c r="F68" t="s">
+        <v>563</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>565</v>
+      </c>
+      <c r="B69" t="s">
+        <v>566</v>
+      </c>
+      <c r="C69" t="s">
+        <v>258</v>
+      </c>
+      <c r="D69" t="s">
+        <v>432</v>
+      </c>
+      <c r="E69" t="s">
+        <v>567</v>
+      </c>
+      <c r="F69" t="s">
+        <v>568</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>570</v>
+      </c>
+      <c r="B70" t="s">
+        <v>566</v>
+      </c>
+      <c r="C70" t="s">
+        <v>258</v>
+      </c>
+      <c r="D70" t="s">
+        <v>432</v>
+      </c>
+      <c r="E70" t="s">
+        <v>567</v>
+      </c>
+      <c r="F70" t="s">
+        <v>571</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>573</v>
+      </c>
+      <c r="B71" t="s">
+        <v>574</v>
+      </c>
+      <c r="C71" t="s">
+        <v>258</v>
+      </c>
+      <c r="D71" t="s">
+        <v>234</v>
+      </c>
+      <c r="E71" t="s">
+        <v>575</v>
+      </c>
+      <c r="F71" t="s">
+        <v>576</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>578</v>
+      </c>
+      <c r="B72" t="s">
+        <v>579</v>
+      </c>
+      <c r="C72" t="s">
+        <v>311</v>
+      </c>
+      <c r="D72" t="s">
+        <v>234</v>
+      </c>
+      <c r="E72" t="s">
+        <v>580</v>
+      </c>
+      <c r="F72" t="s">
+        <v>581</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>583</v>
+      </c>
+      <c r="B73" t="s">
+        <v>584</v>
+      </c>
+      <c r="C73" t="s">
+        <v>585</v>
+      </c>
+      <c r="D73" t="s">
+        <v>234</v>
+      </c>
+      <c r="E73" t="s">
+        <v>228</v>
+      </c>
+      <c r="F73" t="s">
+        <v>586</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-16.xlsx
+++ b/docs/xlsx/jobs-2026-10-16.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="859">
   <si>
     <t>Title</t>
   </si>
@@ -709,6 +709,27 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/land-conservation-manager-3/</t>
   </si>
   <si>
+    <t>4th Grade Teacher</t>
+  </si>
+  <si>
+    <t>St. James School Philadelphia</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb361d1392bc4e438b5a690184e3c0e6-4th-grade-teacher-st-james-school-philadelphia-philadelphia</t>
+  </si>
+  <si>
     <t>Ability:IMPACT Program Coordinator</t>
   </si>
   <si>
@@ -718,9 +739,6 @@
     <t>Boston, Massachusetts</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 62000.00 - 62000.00/year</t>
   </si>
   <si>
@@ -748,6 +766,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/50a42a449f9740648e862af652029d6b-administrative-assistant-to-the-evpchief-programs-fellowships-officer-cs-princeton</t>
   </si>
   <si>
+    <t>Advancement Assistant</t>
+  </si>
+  <si>
+    <t>WildCare</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73429ed551ac45799bed5cfbdd8e8825-advancement-assistant-wildcare-san-rafael</t>
+  </si>
+  <si>
     <t>Advocacy Director</t>
   </si>
   <si>
@@ -766,6 +805,39 @@
     <t>https://www.idealist.org/en/government-job/f070074202ff444b94a176c9cf07d64a-advocacy-director-mental-health-legal-advisors-committee-quincy</t>
   </si>
   <si>
+    <t>Annual Giving Officer</t>
+  </si>
+  <si>
+    <t>Protect Democracy</t>
+  </si>
+  <si>
+    <t>USD 84300.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4cd67993b1b42f6a348c525ab86aba3-annual-giving-officer-protect-democracy-washington</t>
+  </si>
+  <si>
+    <t>Assistant Vice President of Property Management - Administration</t>
+  </si>
+  <si>
+    <t>King County Housing Authority</t>
+  </si>
+  <si>
+    <t>Tukwila, Washington</t>
+  </si>
+  <si>
+    <t>USD 144695.00 - 202571.78/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29145cda01a940fe9593e3acba744da8-assistant-vice-president-of-property-management-administration-king-county-housing-authority-tukwila</t>
+  </si>
+  <si>
     <t>Associate Community Organizer</t>
   </si>
   <si>
@@ -802,6 +874,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/4078355dd20d44d6901070471cbfb710-associate-director-of-communications-transportation-alternatives-new-york</t>
   </si>
   <si>
+    <t>Associate Vice President, Principal Gifts</t>
+  </si>
+  <si>
+    <t>Lucile Packard Foundation for Children's Health</t>
+  </si>
+  <si>
+    <t>Palo Alto, CA</t>
+  </si>
+  <si>
+    <t>USD 280000.00 - 300000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb7348556f6b47249f03d4ab3e8a4570-associate-vice-president-principal-gifts-lucile-packard-foundation-for-childrens-health-palo-alto</t>
+  </si>
+  <si>
     <t>Associate, Conferences and Events</t>
   </si>
   <si>
@@ -820,6 +910,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/3ed1f2a277d9430598446c8f3452911b-associate-conferences-and-events-council-on-foundations-washington</t>
   </si>
   <si>
+    <t>Attorney, Women’s Defense Project, Criminal Defense Practice</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f3243a08863401ab2ded360d90e6fce-attorney-womens-defense-project-criminal-defense-practice-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
     <t>Bilingual Paralegal - Social Security Income (SSI)</t>
   </si>
   <si>
@@ -856,6 +964,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/de7467d9b1ef4ab9a3480e2a5ea2701e-building-supervisor-linworth-united-methodist-church-columbus</t>
   </si>
   <si>
+    <t>Cancer Screening Program Coordinator - Bilingual (Spanish)</t>
+  </si>
+  <si>
+    <t>Neighborhood Health</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d9d482e79e21433888a4444bd8b03f92-cancer-screening-program-coordinator-bilingual-spanish-neighborhood-health-alexandria</t>
+  </si>
+  <si>
     <t>Case Manager</t>
   </si>
   <si>
@@ -874,6 +1000,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/6b2d0b5bcf354d599a5403934c42cf27-case-manager-ace-association-of-community-employment-programs-for-the-homeless-inc-queens-county</t>
   </si>
   <si>
+    <t>Case Manager II- Bilingual in Ukrainian</t>
+  </si>
+  <si>
+    <t>Neighborhood House</t>
+  </si>
+  <si>
+    <t>USD 31.48 - 34.90/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/357b1871c76648d380520a29b48d4109-case-manager-ii-bilingual-in-ukrainian-neighborhood-house-tukwila</t>
+  </si>
+  <si>
     <t>Chief Financial Officer</t>
   </si>
   <si>
@@ -904,6 +1045,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/f02f6d1451784035a1788a0fe5d4ff03-chief-operating-officer-animal-advocacy-careers-london</t>
   </si>
   <si>
+    <t>Chief Operating Officer (COO)</t>
+  </si>
+  <si>
+    <t>American Bridge 21st Century</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/805bd340bea14870bb08c3e8a15d11e7-chief-operating-officer-coo-american-bridge-21st-century-washington</t>
+  </si>
+  <si>
+    <t>Civic Engagement Strategist</t>
+  </si>
+  <si>
+    <t>Native American Youth and Family Center (NAYA)</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0fa3af6901cd4427afd91a7d6eab4d64-civic-engagement-strategist-native-american-youth-and-family-center-naya-portland</t>
+  </si>
+  <si>
+    <t>Client Advocate, Women’s Defense Project, Criminal Defense Practice</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/67a8957f017940038fd3db58a95d3141-client-advocate-womens-defense-project-criminal-defense-practice-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
     <t>Communications Consultant</t>
   </si>
   <si>
@@ -925,6 +1108,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/87db713c009240dd91c1903698760548-communications-consultant-greenroots-inc-chelsea</t>
   </si>
   <si>
+    <t>Communications Manager (Hybrid)</t>
+  </si>
+  <si>
+    <t>Pathways to Housing DC</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e01d221baf244f7da8524f50d4935668-communications-manager-hybrid-pathways-to-housing-dc-washington</t>
+  </si>
+  <si>
+    <t>Community Defense Staff Attorney</t>
+  </si>
+  <si>
+    <t>The Immigrant Law Center of Minnesota</t>
+  </si>
+  <si>
+    <t>Saint Paul, MN</t>
+  </si>
+  <si>
+    <t>USD 84800.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73db4ec2938d434cb44e59867a481264-community-defense-staff-attorney-the-immigrant-law-center-of-minnesota-saint-paul</t>
+  </si>
+  <si>
     <t>Community Relations Coordinator</t>
   </si>
   <si>
@@ -1000,6 +1216,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/143af854372b49ef85997036fc217448-cuidadorases-sociales-para-el-programa-de-obera-aldeas-infantiles-sos-argentina-obera</t>
   </si>
   <si>
+    <t>Culinary Education Manager II</t>
+  </si>
+  <si>
+    <t>Mandela Partners</t>
+  </si>
+  <si>
+    <t>San Leandro, California</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b90a47c1c8d540cb847e1f2753cbbc1e-culinary-education-manager-ii-mandela-partners-san-leandro</t>
+  </si>
+  <si>
+    <t>Cultural Exchange Associate</t>
+  </si>
+  <si>
+    <t>American Cultural Exchange Service</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 22.25/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab87fcd2d64d4834ac260f6cbcba9a25-cultural-exchange-associate-american-cultural-exchange-service-portland</t>
+  </si>
+  <si>
     <t>Data Analyst</t>
   </si>
   <si>
@@ -1018,6 +1267,93 @@
     <t>https://www.idealist.org/en/nonprofit-job/c82affff8bff42c2885e1f9e08c65cc4-data-analyst-unite-america-denver</t>
   </si>
   <si>
+    <t>Eviction Defense Collaborative</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 32.42 - 37.47/hour</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c2106bc0dc642239b2c1bb8c83ccc9c-data-analyst-eviction-defense-collaborative-san-francisco</t>
+  </si>
+  <si>
+    <t>Development &amp; Communications Coordinator</t>
+  </si>
+  <si>
+    <t>La Vida Scholars</t>
+  </si>
+  <si>
+    <t>Lynn, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e004a5a8ea1d4c9188d196c41206d245-development-communications-coordinator-la-vida-scholars-lynn</t>
+  </si>
+  <si>
+    <t>Development and Communications Coordinator</t>
+  </si>
+  <si>
+    <t>Summer Search</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 37.31 - 39.68/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b0862d023a64b50a76a837cf3ecc560-development-and-communications-coordinator-summer-search-oakland</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>Flatbush Cats</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 66500.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9269952f01d4df499bcb6318991403b-development-associate-flatbush-cats-kings-county</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Tillamook Estuaries Partnership</t>
+  </si>
+  <si>
+    <t>Garibaldi, Oregon</t>
+  </si>
+  <si>
+    <t>USD 60300.00 - 71900.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e33977ee4b9f48a3825f8dbab9938606-development-coordinator-tillamook-estuaries-partnership-garibaldi</t>
+  </si>
+  <si>
     <t>Development Director</t>
   </si>
   <si>
@@ -1048,6 +1384,39 @@
     <t>https://www.idealist.org/en/business-job/81156b473f78408c84f814894050e4e9-digital-marketing-social-media-specialist-global-culture-network-abuja</t>
   </si>
   <si>
+    <t>Digital Strategy &amp; Engagement Manager</t>
+  </si>
+  <si>
+    <t>Northwest Harvest</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 35.75 - 39.75/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4fdf9eca51b24564b7fbd8c435c1f4b5-digital-strategy-engagement-manager-northwest-harvest-seattle</t>
+  </si>
+  <si>
+    <t>Director of Development &amp; Community Engagement</t>
+  </si>
+  <si>
+    <t>Nashua Police Athletic League</t>
+  </si>
+  <si>
+    <t>Nashua, New Hampshire</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/32ca8e4c12a248baab7d552c07bd1e41-director-of-development-community-engagement-nashua-police-athletic-league-nashua</t>
+  </si>
+  <si>
     <t>Director of Development &amp; Fundraising</t>
   </si>
   <si>
@@ -1081,6 +1450,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/3ad4890c9e924e3fb19e01b40c433da1-director-of-development-and-finance-interfaith-philadelphia-philadelphia</t>
   </si>
   <si>
+    <t>Director of Housing Acquisition + Unit Readiness</t>
+  </si>
+  <si>
+    <t>Anthos Home</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b9080d94cd9648e1a91f03b3c681d2aa-director-of-housing-acquisition-unit-readiness-anthos-home-new-york</t>
+  </si>
+  <si>
+    <t>Director of Philanthropic Marketing &amp; Engagement</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters of New York City</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16d69fa32e9144968278f9acf5b87baa-director-of-philanthropic-marketing-engagement-big-brothers-big-sisters-of-new-york-city-new-york</t>
+  </si>
+  <si>
     <t>Director of Research</t>
   </si>
   <si>
@@ -1114,9 +1507,6 @@
     <t>Director of Youth Ministries</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 19000.00 - 22000.00/year</t>
   </si>
   <si>
@@ -1135,6 +1525,39 @@
     <t>https://www.idealist.org/en/job/c807582318084bd7842148940154b1d2-director-programs-resources-for-abortion-delivery-washington</t>
   </si>
   <si>
+    <t>Director, School Partnerships &amp; Coaching</t>
+  </si>
+  <si>
+    <t>College Success Foundation</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>USD 103229.00 - 154843.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe21349bf6c14bb9b6a308668e8cc1e3-director-school-partnerships-coaching-college-success-foundation-bellevue</t>
+  </si>
+  <si>
+    <t>Donor Impact Officer</t>
+  </si>
+  <si>
+    <t>United Way of King County (WA State)</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 35.27 - 37.17/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/613d56fe625e4587b9cd2edba44d6221-donor-impact-officer-united-way-of-king-county-wa-state-seattle</t>
+  </si>
+  <si>
     <t>Early Childhood Center Office Administrator</t>
   </si>
   <si>
@@ -1147,12 +1570,27 @@
     <t>USD 50000.00 - 60000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d9fea987dc07443992b7a02fc0ad2939-early-childhood-center-office-administrator-bender-jcc-early-childhood-center-rockville</t>
   </si>
   <si>
+    <t>Education Fellow / Program Coordinator</t>
+  </si>
+  <si>
+    <t>Case Method Institute for Education and Democracy</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6164bfb3f694c1b852e9a2df048db49-education-fellow-program-coordinator-case-method-institute-for-education-and-democracy-cambridge</t>
+  </si>
+  <si>
     <t>Elementary Math Teaching Assistant for After School Club</t>
   </si>
   <si>
@@ -1168,6 +1606,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/524b9a1b186b4457aa6552e570eed427-elementary-math-teaching-assistant-for-after-school-club-the-art-of-problem-solving-initiative-inc-new-york</t>
   </si>
   <si>
+    <t>Evening/ Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Children's Arts &amp; Science Workshops, Inc.</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87f85454fadd4833afbcc627c5c402a3-evening-outreach-coordinator-childrens-arts-science-workshops-inc-new-york</t>
+  </si>
+  <si>
     <t>HealthQ</t>
   </si>
   <si>
@@ -1183,6 +1636,21 @@
     <t>https://www.idealist.org/en/job/f7060cc96413483080b5292d445d43b4-executive-director-healthq-haverhill</t>
   </si>
   <si>
+    <t>Henry L Ferguson Museum</t>
+  </si>
+  <si>
+    <t>Fishers Island, New York</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35704b9cfd6e41ac92ce67b158e9d6ca-executive-director-henry-l-ferguson-museum-fishers-island</t>
+  </si>
+  <si>
     <t>Executive Director, Compost Research &amp; Education Foundation (CREF)</t>
   </si>
   <si>
@@ -1192,9 +1660,6 @@
     <t>Remote (North Carolina)</t>
   </si>
   <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>Agriculture, Climate Change, Education</t>
   </si>
   <si>
@@ -1249,6 +1714,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/ecb4ad1454194174823923786576fd07-family-service-worker-youth-villages-nashville</t>
   </si>
   <si>
+    <t>Finance &amp; Operations Manager</t>
+  </si>
+  <si>
+    <t>Horton's Kids, Inc.</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2f899d3c20e42f591a2b4af587441e9-finance-operations-manager-hortons-kids-inc-washington</t>
+  </si>
+  <si>
+    <t>Fractional Nonprofit Financial Consultant (Grant Administration &amp; Accounting)</t>
+  </si>
+  <si>
+    <t>Wealth4Impact</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b7b7095a2854f63b2f706a041e4999d-fractional-nonprofit-financial-consultant-grant-administration-accounting-wealth4impact-ellicott-city</t>
+  </si>
+  <si>
     <t>Full-time Program Director</t>
   </si>
   <si>
@@ -1279,6 +1768,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/872279cba7bf43708029af8edb93feee-grant-writer-friends-of-the-stone-church-the-stone-church-cultural-center-gilbertville</t>
   </si>
   <si>
+    <t>Group Leader [Bronx]</t>
+  </si>
+  <si>
+    <t>Replications, Inc</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39ed9d15aa974adba06f34db336dc4fe-group-leader-bronx-replications-inc-bronx</t>
+  </si>
+  <si>
+    <t>Group Leader [Brooklyn]</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/44bd9c30e85a48daaa1362b1f1f36009-group-leader-brooklyn-replications-inc-brooklyn</t>
+  </si>
+  <si>
+    <t>Health Insurance Navigator/Immigrant Community Outreach Worker</t>
+  </si>
+  <si>
+    <t>Centro Comunitario CEUS</t>
+  </si>
+  <si>
+    <t>North Bergen, New Jersey</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 21.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8a4822406da04d5abe0b58bf0bb6f1ff-health-insurance-navigatorimmigrant-community-outreach-worker-centro-comunitario-ceus-north-bergen</t>
+  </si>
+  <si>
+    <t>High School STEM Tutor</t>
+  </si>
+  <si>
+    <t>Japanese Community Youth Council</t>
+  </si>
+  <si>
+    <t>USD 23.50 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1cc8559a52554f728b548a64db22fd09-high-school-stem-tutor-japanese-community-youth-council-san-francisco</t>
+  </si>
+  <si>
     <t>Housing Staff Attorney</t>
   </si>
   <si>
@@ -1303,6 +1852,27 @@
     <t>https://www.idealist.org/en/business-job/5b5e03eaed234d0b80b852ec3e31a9b2-hr-manager-global-culture-network-abuja</t>
   </si>
   <si>
+    <t>Impact &amp; Evaluation Data Analyst</t>
+  </si>
+  <si>
+    <t>Oakland Promise</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40969ca86389435bb0a50b16f25d0def-impact-evaluation-data-analyst-oakland-promise-oakland</t>
+  </si>
+  <si>
+    <t>Individual Giving Manager (Hybrid)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0173ca9fc0f44ee0802fb15c47b2d573-individual-giving-manager-hybrid-pathways-to-housing-dc-washington</t>
+  </si>
+  <si>
     <t>JOIN A PROGRESSIVE CAMPAIGN IN CALIFORNIA’S 48TH CONGRESSIONAL DISTRICT!</t>
   </si>
   <si>
@@ -1324,6 +1894,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/604688e58bb54e73b543581ed409e26a-join-a-progressive-campaign-in-californias-48th-congressional-district-worker-power-murrieta</t>
   </si>
   <si>
+    <t>Moreno Valley, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26f7b5393504452e9ba2f64131e77d77-join-a-progressive-campaign-in-californias-48th-congressional-district-worker-power-moreno-valley</t>
+  </si>
+  <si>
     <t>Legal Advocate</t>
   </si>
   <si>
@@ -1381,15 +1957,9 @@
     <t>Jewish Community Council of Greater Coney Island</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 95000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d7d95e12971c468ca55bd231714a0a0d-manager-marketing-communications-and-external-affairs-jewish-community-council-of-greater-coney-island-kings-county</t>
   </si>
   <si>
@@ -1447,6 +2017,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/563c82a4a5404dcaad796c6d93844e40-marketing-project-manager-campus-experiences-national-geographic-society-washington</t>
   </si>
   <si>
+    <t>Membership Recruitment Specialist</t>
+  </si>
+  <si>
+    <t>Girl Scout Council of the Nation's Capital</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7abdde6c58f6447f995a8282c71e3226-membership-recruitment-specialist-girl-scout-council-of-the-nations-capital-alexandria</t>
+  </si>
+  <si>
     <t>NY Renews Coalition Organizer</t>
   </si>
   <si>
@@ -1489,6 +2071,18 @@
     <t>https://www.idealist.org/en/job/52d5e073b0a24c40a1582a7813275ae5-officer-state-decarbonization-campaign-lead-pew-charitable-trusts-washington</t>
   </si>
   <si>
+    <t>Operations Director -- Make the Road PA</t>
+  </si>
+  <si>
+    <t>Alina Sipp-Alpers Consulting</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4af9f6fc8dee436980ccec157103386d-operations-director-make-the-road-pa-alina-sipp-alpers-consulting-philadelphia</t>
+  </si>
+  <si>
     <t>Operations Manager</t>
   </si>
   <si>
@@ -1507,6 +2101,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/00e76af545dc460480e3fcc71e8cdfd9-operations-manager-mid-ohio-market-reynoldsburg</t>
   </si>
   <si>
+    <t>Paralegal, Women’s Defense Project, Criminal Defense Practice</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08e7f83eceed4fa9a795779f0fd31d09-paralegal-womens-defense-project-criminal-defense-practice-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
     <t>Part-time Assistant Resident Manager</t>
   </si>
   <si>
@@ -1534,12 +2134,18 @@
     <t>USD 215378.00 - 215378.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Education, Philanthropy</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/a960c1ca1e364aa18a3b870a4b842a60-partner-external-relations-education-forward-dc-washington</t>
   </si>
   <si>
+    <t>People Operations Manager</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8642e9f71a2a4deebc803dd8cc5827c5-people-operations-manager-flatbush-cats-kings-county</t>
+  </si>
+  <si>
     <t>Philanthropy Operations Manager</t>
   </si>
   <si>
@@ -1552,9 +2158,6 @@
     <t>USD 62000.00 - 65000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Economic Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/61592af416b84c9bb2facc0deb20734c-philanthropy-operations-manager-covenant-house-michigan-detroit</t>
   </si>
   <si>
@@ -1570,12 +2173,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/9368a1529c8e46f990697ff4c21287f0-prestadora-de-servicios-de-mantenimiento-aldeas-infantiles-sos-argentina-mar-del-plata</t>
   </si>
   <si>
+    <t>Program Assistant, China AI Initiative</t>
+  </si>
+  <si>
+    <t>Carnegie Endowment for International Peace</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/abcc1a4fd72f4f11a37e52739444bf5b-program-assistant-china-ai-initiative-carnegie-endowment-for-international-peace-washington</t>
+  </si>
+  <si>
     <t>Program Associate, Youth Engagement</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/ee7f13e4e72b4d26b6e1261e146a1d20-program-associate-youth-engagement-cs-princeton</t>
   </si>
   <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>PORTLAND LITERACY COUNCIL INC</t>
+  </si>
+  <si>
+    <t>Remote (Portland, Oregon)</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b33240ccd74b43c1b5820d9780140d08-program-coordinator-portland-literacy-council-inc-portland</t>
+  </si>
+  <si>
     <t>Program Director, Feeding Our Neighbors (FON)</t>
   </si>
   <si>
@@ -1591,6 +2224,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c1c1578a97614cb1b02ad64fb29648df-program-director-feeding-our-neighbors-fon-catholic-charities-archdiocese-of-ny-bronx-county</t>
   </si>
   <si>
+    <t>Program Manager, South (Kentucky)</t>
+  </si>
+  <si>
+    <t>Generation Citizen</t>
+  </si>
+  <si>
+    <t>USD 66120.00 - 66120.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a3845cac4944029b924ad0bfb658ff9-program-manager-south-kentucky-generation-citizen-new-york</t>
+  </si>
+  <si>
+    <t>Program Manager, South (North Carolina)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a9d4abe2a5d47f195117ed7fcbcbfb5-program-manager-south-north-carolina-generation-citizen-new-york</t>
+  </si>
+  <si>
     <t>Program Officer, Social Impact</t>
   </si>
   <si>
@@ -1603,18 +2254,75 @@
     <t>https://www.idealist.org/en/nonprofit-job/80d9627e464a493bae29a8b7f3e2ab1d-program-officer-social-impact-panorama-global-new-york</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/6e66b6e02fe64f349e339ebaeb1b7fc8-program-officer-social-impact-panorama-global-seattle</t>
   </si>
   <si>
+    <t>Public Policy and Advocacy Organizer</t>
+  </si>
+  <si>
+    <t>ACLU of Connecticut</t>
+  </si>
+  <si>
+    <t>Hartford, CT</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8afd1005d594f24bcd8438eab913300-public-policy-and-advocacy-organizer-aclu-of-connecticut-hartford</t>
+  </si>
+  <si>
+    <t>Research Associate</t>
+  </si>
+  <si>
+    <t>Bell Policy Center</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/174b0e7795ea42d3a4f1a4177414d96f-research-associate-bell-policy-center-denver</t>
+  </si>
+  <si>
+    <t>Residential Coordinator</t>
+  </si>
+  <si>
+    <t>WeAchieve Inc</t>
+  </si>
+  <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e95ab52b2b44edfade2396afb8a1e6b-residential-coordinator-weachieve-inc-silver-spring</t>
+  </si>
+  <si>
+    <t>Safe Haven Program Manager</t>
+  </si>
+  <si>
+    <t>Swords to Plowshares: A Veterans Rights Organization, San Francisco, CA</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8c65c8a8d48453a84079428334aeb58-safe-haven-program-manager-swords-to-plowshares-a-veterans-rights-organization-san-francisco-ca-san-francisco</t>
+  </si>
+  <si>
     <t>School Based Advisor</t>
   </si>
   <si>
-    <t>College Success Foundation</t>
-  </si>
-  <si>
     <t>Tacoma, Washington</t>
   </si>
   <si>
@@ -1624,6 +2332,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/afa5f2d111e24bf9976d825d37807f25-school-based-advisor-college-success-foundation-tacoma</t>
   </si>
   <si>
+    <t>Science Ambassador Fellow</t>
+  </si>
+  <si>
+    <t>Union of Concerned Scientists</t>
+  </si>
+  <si>
+    <t>USD 109232.02 - 109232.02/year</t>
+  </si>
+  <si>
+    <t>Environment, Research Social Science, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b9042d8f82854aed9c13cbf00fc8da51-science-ambassador-fellow-union-of-concerned-scientists-cambridge</t>
+  </si>
+  <si>
+    <t>Senior Associate, Policy</t>
+  </si>
+  <si>
+    <t>American Public Human Services Association</t>
+  </si>
+  <si>
+    <t>USD 76500.00 - 86500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30f28c5ead4f4fd6a3aba0df50050323-senior-associate-policy-american-public-human-services-association-arlington</t>
+  </si>
+  <si>
     <t>Senior Client Services Coordinator</t>
   </si>
   <si>
@@ -1687,12 +2422,66 @@
     <t>https://www.idealist.org/en/job/0d3036187fd442a3b20df56add314451-senior-specialist-operations-chef-ann-foundation-boulder</t>
   </si>
   <si>
+    <t>Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>Partnership for Civil Justice</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2da741774eb44eeba50186e4973b9a4-senior-staff-attorney-partnership-for-civil-justice-washington</t>
+  </si>
+  <si>
+    <t>Site Director - Silicon Valley</t>
+  </si>
+  <si>
+    <t>SquashDrive</t>
+  </si>
+  <si>
+    <t>Redwood City, California</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/85a43546597e49549cb9f47a81e7421f-site-director-silicon-valley-squashdrive-redwood-city</t>
+  </si>
+  <si>
+    <t>Special Projects Coordinator</t>
+  </si>
+  <si>
+    <t>The Episcopal Diocese of New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f38443973e504cb197e21c612e3e3657-special-projects-coordinator-the-episcopal-diocese-of-new-york-new-york</t>
+  </si>
+  <si>
     <t>Specialist, Operations</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/job/01171c14d95c4452b2690381e6aba40a-specialist-operations-chef-ann-foundation-boulder</t>
   </si>
   <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30121da40f7d490c9ad92d90f16bc493-staff-attorney-partnership-for-civil-justice-washington</t>
+  </si>
+  <si>
     <t>State Organizer for Texas (Hunger and Poverty Advocacy)</t>
   </si>
   <si>
@@ -1711,6 +2500,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/3e8eb533799446c19a2fa69e3fae8903-state-organizer-for-texas-hunger-and-poverty-advocacy-bread-for-the-world-inc-houston</t>
   </si>
   <si>
+    <t>Strategic Initiatives Director</t>
+  </si>
+  <si>
+    <t>Tipping Point Community</t>
+  </si>
+  <si>
+    <t>USD 193000.00 - 193000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2488a0a80be14c208dcfcd758b041935-strategic-initiatives-director-tipping-point-community-san-francisco</t>
+  </si>
+  <si>
+    <t>Termes de référence de la consultance: Pérennité organisationnelle, Côte d’Ivoire et Guinée</t>
+  </si>
+  <si>
+    <t>Global Fund for Children</t>
+  </si>
+  <si>
+    <t>Remote (CI)</t>
+  </si>
+  <si>
+    <t>USD 150.00 - 200.00/day</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/03a3b6eff1044efc8f6d5a4002084f71-termes-de-reference-de-la-consultance-perennite-organisationnelle-cote-divoire-et-guinee-global-fund-for-children-washington</t>
+  </si>
+  <si>
     <t>The Pauli Murray Fellowship, Communications Team</t>
   </si>
   <si>
@@ -1729,9 +2548,6 @@
     <t>The Pauli Murray Fellowship, EDIB Team</t>
   </si>
   <si>
-    <t>Human Rights Civil Liberties</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/f7a7ab571c944abcb7eb57845afa2ee1-the-pauli-murray-fellowship-edib-team-american-civil-liberties-union-new-york</t>
   </si>
   <si>
@@ -1769,9 +2585,6 @@
   </si>
   <si>
     <t>Small Things, Inc.</t>
-  </si>
-  <si>
-    <t>Philadelphia, Pennsylvania</t>
   </si>
   <si>
     <t>Community Development, Economic Development, Housing Homelessness</t>
@@ -3295,7 +4108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3414,50 +4227,50 @@
         <v>252</v>
       </c>
       <c r="D5" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="E5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
         <v>234</v>
       </c>
       <c r="E6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C7" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="D7" t="s">
         <v>234</v>
@@ -3572,671 +4385,671 @@
         <v>293</v>
       </c>
       <c r="C12" t="s">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="D12" t="s">
         <v>234</v>
       </c>
       <c r="E12" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="F12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D13" t="s">
-        <v>299</v>
+        <v>234</v>
       </c>
       <c r="E13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D14" t="s">
         <v>234</v>
       </c>
       <c r="E14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D15" t="s">
         <v>234</v>
       </c>
       <c r="E15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D16" t="s">
         <v>234</v>
       </c>
       <c r="E16" t="s">
-        <v>228</v>
+        <v>319</v>
       </c>
       <c r="F16" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B17" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="C17" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D17" t="s">
         <v>234</v>
       </c>
       <c r="E17" t="s">
-        <v>228</v>
+        <v>325</v>
       </c>
       <c r="F17" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B18" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="C18" t="s">
-        <v>325</v>
+        <v>270</v>
       </c>
       <c r="D18" t="s">
         <v>234</v>
       </c>
       <c r="E18" t="s">
-        <v>228</v>
+        <v>330</v>
       </c>
       <c r="F18" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B19" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C19" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D19" t="s">
         <v>234</v>
       </c>
       <c r="E19" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F19" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B20" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C20" t="s">
-        <v>336</v>
+        <v>246</v>
       </c>
       <c r="D20" t="s">
         <v>234</v>
       </c>
       <c r="E20" t="s">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="F20" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B21" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C21" t="s">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="D21" t="s">
         <v>234</v>
       </c>
       <c r="E21" t="s">
-        <v>228</v>
+        <v>345</v>
       </c>
       <c r="F21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B22" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C22" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D22" t="s">
         <v>234</v>
       </c>
       <c r="E22" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F22" t="s">
-        <v>228</v>
+        <v>352</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B23" t="s">
-        <v>350</v>
+        <v>299</v>
       </c>
       <c r="C23" t="s">
-        <v>351</v>
+        <v>300</v>
       </c>
       <c r="D23" t="s">
         <v>234</v>
       </c>
       <c r="E23" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F23" t="s">
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B24" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C24" t="s">
-        <v>240</v>
+        <v>359</v>
       </c>
       <c r="D24" t="s">
-        <v>234</v>
+        <v>360</v>
       </c>
       <c r="E24" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F24" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B25" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="D25" t="s">
         <v>234</v>
       </c>
       <c r="E25" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F25" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B26" t="s">
-        <v>275</v>
+        <v>370</v>
       </c>
       <c r="C26" t="s">
-        <v>276</v>
+        <v>371</v>
       </c>
       <c r="D26" t="s">
-        <v>366</v>
+        <v>234</v>
       </c>
       <c r="E26" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F26" t="s">
-        <v>278</v>
+        <v>373</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B27" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C27" t="s">
-        <v>240</v>
+        <v>377</v>
       </c>
       <c r="D27" t="s">
         <v>234</v>
       </c>
       <c r="E27" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="F27" t="s">
-        <v>228</v>
+        <v>379</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B28" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C28" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="D28" t="s">
         <v>234</v>
       </c>
       <c r="E28" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F28" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B29" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C29" t="s">
-        <v>311</v>
+        <v>389</v>
       </c>
       <c r="D29" t="s">
-        <v>366</v>
+        <v>234</v>
       </c>
       <c r="E29" t="s">
-        <v>381</v>
+        <v>228</v>
       </c>
       <c r="F29" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>392</v>
       </c>
       <c r="B30" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C30" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D30" t="s">
         <v>234</v>
       </c>
       <c r="E30" t="s">
-        <v>386</v>
+        <v>228</v>
       </c>
       <c r="F30" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B31" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C31" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="D31" t="s">
         <v>234</v>
       </c>
       <c r="E31" t="s">
-        <v>392</v>
+        <v>228</v>
       </c>
       <c r="F31" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B32" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C32" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D32" t="s">
         <v>234</v>
       </c>
       <c r="E32" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F32" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B33" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C33" t="s">
-        <v>401</v>
+        <v>350</v>
       </c>
       <c r="D33" t="s">
         <v>234</v>
       </c>
       <c r="E33" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="F33" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B34" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C34" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D34" t="s">
         <v>234</v>
       </c>
       <c r="E34" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="F34" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B35" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="C35" t="s">
-        <v>346</v>
+        <v>418</v>
       </c>
       <c r="D35" t="s">
         <v>234</v>
       </c>
       <c r="E35" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="F35" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B36" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="C36" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="D36" t="s">
         <v>234</v>
       </c>
       <c r="E36" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="F36" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B37" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="C37" t="s">
-        <v>240</v>
+        <v>430</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="E37" t="s">
-        <v>228</v>
+        <v>431</v>
       </c>
       <c r="F37" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="B38" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="C38" t="s">
-        <v>311</v>
+        <v>436</v>
       </c>
       <c r="D38" t="s">
         <v>234</v>
       </c>
       <c r="E38" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="F38" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="B39" t="s">
-        <v>341</v>
+        <v>441</v>
       </c>
       <c r="C39" t="s">
-        <v>240</v>
+        <v>442</v>
       </c>
       <c r="D39" t="s">
         <v>234</v>
       </c>
       <c r="E39" t="s">
-        <v>228</v>
+        <v>443</v>
       </c>
       <c r="F39" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="B40" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="C40" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="D40" t="s">
-        <v>432</v>
+        <v>234</v>
       </c>
       <c r="E40" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="F40" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="B41" t="s">
-        <v>245</v>
+        <v>453</v>
       </c>
       <c r="C41" t="s">
         <v>246</v>
@@ -4245,749 +5058,2083 @@
         <v>234</v>
       </c>
       <c r="E41" t="s">
-        <v>437</v>
+        <v>228</v>
       </c>
       <c r="F41" t="s">
-        <v>248</v>
+        <v>454</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="B42" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="C42" t="s">
-        <v>240</v>
+        <v>458</v>
       </c>
       <c r="D42" t="s">
         <v>234</v>
       </c>
       <c r="E42" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="F42" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="B43" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="C43" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="D43" t="s">
         <v>234</v>
       </c>
       <c r="E43" t="s">
-        <v>228</v>
+        <v>465</v>
       </c>
       <c r="F43" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="B44" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="C44" t="s">
-        <v>264</v>
+        <v>469</v>
       </c>
       <c r="D44" t="s">
         <v>234</v>
       </c>
       <c r="E44" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="F44" t="s">
         <v>228</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="B45" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="C45" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="D45" t="s">
         <v>234</v>
       </c>
       <c r="E45" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="F45" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="B46" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="C46" t="s">
-        <v>461</v>
+        <v>383</v>
       </c>
       <c r="D46" t="s">
         <v>234</v>
       </c>
       <c r="E46" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="F46" t="s">
-        <v>463</v>
+        <v>272</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="B47" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="C47" t="s">
-        <v>467</v>
+        <v>383</v>
       </c>
       <c r="D47" t="s">
         <v>234</v>
       </c>
       <c r="E47" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="F47" t="s">
-        <v>469</v>
+        <v>352</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="B48" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="C48" t="s">
-        <v>473</v>
+        <v>246</v>
       </c>
       <c r="D48" t="s">
         <v>234</v>
       </c>
       <c r="E48" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="F48" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="B49" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="C49" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="D49" t="s">
         <v>234</v>
       </c>
       <c r="E49" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="F49" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="B50" t="s">
-        <v>482</v>
+        <v>311</v>
       </c>
       <c r="C50" t="s">
-        <v>483</v>
+        <v>312</v>
       </c>
       <c r="D50" t="s">
-        <v>366</v>
+        <v>253</v>
       </c>
       <c r="E50" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="F50" t="s">
-        <v>485</v>
+        <v>314</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="B51" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C51" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="D51" t="s">
         <v>234</v>
       </c>
       <c r="E51" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="F51" t="s">
         <v>228</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B52" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C52" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="D52" t="s">
         <v>234</v>
       </c>
       <c r="E52" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="F52" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B53" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C53" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D53" t="s">
-        <v>366</v>
+        <v>234</v>
       </c>
       <c r="E53" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="F53" t="s">
-        <v>501</v>
+        <v>228</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B54" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="C54" t="s">
-        <v>264</v>
+        <v>516</v>
       </c>
       <c r="D54" t="s">
         <v>234</v>
       </c>
       <c r="E54" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="F54" t="s">
-        <v>506</v>
+        <v>432</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B55" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="C55" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="D55" t="s">
         <v>234</v>
       </c>
       <c r="E55" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="F55" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B56" t="s">
-        <v>316</v>
+        <v>526</v>
       </c>
       <c r="C56" t="s">
-        <v>515</v>
+        <v>383</v>
       </c>
       <c r="D56" t="s">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="E56" t="s">
-        <v>228</v>
+        <v>527</v>
       </c>
       <c r="F56" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B57" t="s">
-        <v>239</v>
+        <v>531</v>
       </c>
       <c r="C57" t="s">
-        <v>240</v>
+        <v>383</v>
       </c>
       <c r="D57" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="E57" t="s">
-        <v>352</v>
+        <v>532</v>
       </c>
       <c r="F57" t="s">
-        <v>242</v>
+        <v>533</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>520</v>
+        <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="C58" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="D58" t="s">
         <v>234</v>
       </c>
       <c r="E58" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="F58" t="s">
-        <v>495</v>
+        <v>538</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>524</v>
+        <v>539</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>525</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="C59" t="s">
-        <v>311</v>
+        <v>541</v>
       </c>
       <c r="D59" t="s">
         <v>234</v>
       </c>
       <c r="E59" t="s">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="F59" t="s">
-        <v>228</v>
+        <v>543</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="B60" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="C60" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="D60" t="s">
         <v>234</v>
       </c>
       <c r="E60" t="s">
-        <v>527</v>
+        <v>351</v>
       </c>
       <c r="F60" t="s">
-        <v>228</v>
+        <v>548</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>530</v>
+        <v>549</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="B61" t="s">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="C61" t="s">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="D61" t="s">
         <v>234</v>
       </c>
       <c r="E61" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="F61" t="s">
-        <v>506</v>
+        <v>554</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="B62" t="s">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="C62" t="s">
-        <v>311</v>
+        <v>556</v>
       </c>
       <c r="D62" t="s">
         <v>234</v>
       </c>
       <c r="E62" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="F62" t="s">
-        <v>539</v>
+        <v>554</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="B63" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="C63" t="s">
-        <v>240</v>
+        <v>560</v>
       </c>
       <c r="D63" t="s">
         <v>234</v>
       </c>
       <c r="E63" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F63" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="B64" t="s">
-        <v>472</v>
+        <v>551</v>
       </c>
       <c r="C64" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D64" t="s">
         <v>234</v>
       </c>
       <c r="E64" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="F64" t="s">
-        <v>475</v>
+        <v>554</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="B65" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="C65" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="D65" t="s">
         <v>234</v>
       </c>
       <c r="E65" t="s">
-        <v>551</v>
+        <v>351</v>
       </c>
       <c r="F65" t="s">
-        <v>552</v>
+        <v>352</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="B66" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="C66" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D66" t="s">
-        <v>234</v>
+        <v>360</v>
       </c>
       <c r="E66" t="s">
-        <v>228</v>
+        <v>571</v>
       </c>
       <c r="F66" t="s">
-        <v>228</v>
+        <v>572</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="B67" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="C67" t="s">
-        <v>240</v>
+        <v>576</v>
       </c>
       <c r="D67" t="s">
         <v>234</v>
       </c>
       <c r="E67" t="s">
-        <v>228</v>
+        <v>577</v>
       </c>
       <c r="F67" t="s">
-        <v>228</v>
+        <v>578</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="B68" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="C68" t="s">
-        <v>561</v>
+        <v>246</v>
       </c>
       <c r="D68" t="s">
-        <v>234</v>
+        <v>360</v>
       </c>
       <c r="E68" t="s">
-        <v>562</v>
+        <v>228</v>
       </c>
       <c r="F68" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="B69" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="C69" t="s">
-        <v>258</v>
+        <v>586</v>
       </c>
       <c r="D69" t="s">
-        <v>432</v>
+        <v>253</v>
       </c>
       <c r="E69" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="F69" t="s">
-        <v>568</v>
+        <v>352</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="B70" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="C70" t="s">
-        <v>258</v>
+        <v>590</v>
       </c>
       <c r="D70" t="s">
-        <v>432</v>
+        <v>253</v>
       </c>
       <c r="E70" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="F70" t="s">
-        <v>571</v>
+        <v>352</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>572</v>
+        <v>591</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="B71" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="C71" t="s">
-        <v>258</v>
+        <v>594</v>
       </c>
       <c r="D71" t="s">
-        <v>234</v>
+        <v>595</v>
       </c>
       <c r="E71" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="F71" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="B72" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="C72" t="s">
-        <v>311</v>
+        <v>418</v>
       </c>
       <c r="D72" t="s">
-        <v>234</v>
+        <v>595</v>
       </c>
       <c r="E72" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="F72" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="B73" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="C73" t="s">
-        <v>585</v>
+        <v>383</v>
       </c>
       <c r="D73" t="s">
         <v>234</v>
       </c>
       <c r="E73" t="s">
+        <v>606</v>
+      </c>
+      <c r="F73" t="s">
+        <v>607</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>609</v>
+      </c>
+      <c r="B74" t="s">
+        <v>453</v>
+      </c>
+      <c r="C74" t="s">
+        <v>246</v>
+      </c>
+      <c r="D74" t="s">
+        <v>234</v>
+      </c>
+      <c r="E74" t="s">
         <v>228</v>
       </c>
-      <c r="F73" t="s">
-        <v>586</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>587</v>
+      <c r="F74" t="s">
+        <v>610</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>612</v>
+      </c>
+      <c r="B75" t="s">
+        <v>613</v>
+      </c>
+      <c r="C75" t="s">
+        <v>614</v>
+      </c>
+      <c r="D75" t="s">
+        <v>234</v>
+      </c>
+      <c r="E75" t="s">
+        <v>351</v>
+      </c>
+      <c r="F75" t="s">
+        <v>615</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>617</v>
+      </c>
+      <c r="B76" t="s">
+        <v>365</v>
+      </c>
+      <c r="C76" t="s">
+        <v>294</v>
+      </c>
+      <c r="D76" t="s">
+        <v>234</v>
+      </c>
+      <c r="E76" t="s">
+        <v>283</v>
+      </c>
+      <c r="F76" t="s">
+        <v>367</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>619</v>
+      </c>
+      <c r="B77" t="s">
+        <v>620</v>
+      </c>
+      <c r="C77" t="s">
+        <v>621</v>
+      </c>
+      <c r="D77" t="s">
+        <v>622</v>
+      </c>
+      <c r="E77" t="s">
+        <v>623</v>
+      </c>
+      <c r="F77" t="s">
+        <v>624</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>619</v>
+      </c>
+      <c r="B78" t="s">
+        <v>620</v>
+      </c>
+      <c r="C78" t="s">
+        <v>626</v>
+      </c>
+      <c r="D78" t="s">
+        <v>622</v>
+      </c>
+      <c r="E78" t="s">
+        <v>623</v>
+      </c>
+      <c r="F78" t="s">
+        <v>624</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>628</v>
+      </c>
+      <c r="B79" t="s">
+        <v>258</v>
+      </c>
+      <c r="C79" t="s">
+        <v>259</v>
+      </c>
+      <c r="D79" t="s">
+        <v>234</v>
+      </c>
+      <c r="E79" t="s">
+        <v>629</v>
+      </c>
+      <c r="F79" t="s">
+        <v>261</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>631</v>
+      </c>
+      <c r="B80" t="s">
+        <v>632</v>
+      </c>
+      <c r="C80" t="s">
+        <v>246</v>
+      </c>
+      <c r="D80" t="s">
+        <v>234</v>
+      </c>
+      <c r="E80" t="s">
+        <v>633</v>
+      </c>
+      <c r="F80" t="s">
+        <v>634</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>636</v>
+      </c>
+      <c r="B81" t="s">
+        <v>637</v>
+      </c>
+      <c r="C81" t="s">
+        <v>638</v>
+      </c>
+      <c r="D81" t="s">
+        <v>234</v>
+      </c>
+      <c r="E81" t="s">
+        <v>228</v>
+      </c>
+      <c r="F81" t="s">
+        <v>639</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>641</v>
+      </c>
+      <c r="B82" t="s">
+        <v>642</v>
+      </c>
+      <c r="C82" t="s">
+        <v>294</v>
+      </c>
+      <c r="D82" t="s">
+        <v>234</v>
+      </c>
+      <c r="E82" t="s">
+        <v>643</v>
+      </c>
+      <c r="F82" t="s">
+        <v>228</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>645</v>
+      </c>
+      <c r="B83" t="s">
+        <v>646</v>
+      </c>
+      <c r="C83" t="s">
+        <v>436</v>
+      </c>
+      <c r="D83" t="s">
+        <v>234</v>
+      </c>
+      <c r="E83" t="s">
+        <v>647</v>
+      </c>
+      <c r="F83" t="s">
+        <v>352</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>649</v>
+      </c>
+      <c r="B84" t="s">
+        <v>650</v>
+      </c>
+      <c r="C84" t="s">
+        <v>651</v>
+      </c>
+      <c r="D84" t="s">
+        <v>234</v>
+      </c>
+      <c r="E84" t="s">
+        <v>652</v>
+      </c>
+      <c r="F84" t="s">
+        <v>653</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>655</v>
+      </c>
+      <c r="B85" t="s">
+        <v>656</v>
+      </c>
+      <c r="C85" t="s">
+        <v>657</v>
+      </c>
+      <c r="D85" t="s">
+        <v>234</v>
+      </c>
+      <c r="E85" t="s">
+        <v>658</v>
+      </c>
+      <c r="F85" t="s">
+        <v>659</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>661</v>
+      </c>
+      <c r="B86" t="s">
+        <v>662</v>
+      </c>
+      <c r="C86" t="s">
+        <v>663</v>
+      </c>
+      <c r="D86" t="s">
+        <v>234</v>
+      </c>
+      <c r="E86" t="s">
+        <v>664</v>
+      </c>
+      <c r="F86" t="s">
+        <v>665</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>667</v>
+      </c>
+      <c r="B87" t="s">
+        <v>668</v>
+      </c>
+      <c r="C87" t="s">
+        <v>318</v>
+      </c>
+      <c r="D87" t="s">
+        <v>234</v>
+      </c>
+      <c r="E87" t="s">
+        <v>669</v>
+      </c>
+      <c r="F87" t="s">
+        <v>602</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>671</v>
+      </c>
+      <c r="B88" t="s">
+        <v>672</v>
+      </c>
+      <c r="C88" t="s">
+        <v>282</v>
+      </c>
+      <c r="D88" t="s">
+        <v>234</v>
+      </c>
+      <c r="E88" t="s">
+        <v>647</v>
+      </c>
+      <c r="F88" t="s">
+        <v>673</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>675</v>
+      </c>
+      <c r="B89" t="s">
+        <v>676</v>
+      </c>
+      <c r="C89" t="s">
+        <v>677</v>
+      </c>
+      <c r="D89" t="s">
+        <v>253</v>
+      </c>
+      <c r="E89" t="s">
+        <v>678</v>
+      </c>
+      <c r="F89" t="s">
+        <v>679</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>681</v>
+      </c>
+      <c r="B90" t="s">
+        <v>682</v>
+      </c>
+      <c r="C90" t="s">
+        <v>294</v>
+      </c>
+      <c r="D90" t="s">
+        <v>234</v>
+      </c>
+      <c r="E90" t="s">
+        <v>683</v>
+      </c>
+      <c r="F90" t="s">
+        <v>228</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>685</v>
+      </c>
+      <c r="B91" t="s">
+        <v>686</v>
+      </c>
+      <c r="C91" t="s">
+        <v>233</v>
+      </c>
+      <c r="D91" t="s">
+        <v>234</v>
+      </c>
+      <c r="E91" t="s">
+        <v>687</v>
+      </c>
+      <c r="F91" t="s">
+        <v>624</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>689</v>
+      </c>
+      <c r="B92" t="s">
+        <v>690</v>
+      </c>
+      <c r="C92" t="s">
+        <v>691</v>
+      </c>
+      <c r="D92" t="s">
+        <v>234</v>
+      </c>
+      <c r="E92" t="s">
+        <v>692</v>
+      </c>
+      <c r="F92" t="s">
+        <v>693</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>695</v>
+      </c>
+      <c r="B93" t="s">
+        <v>299</v>
+      </c>
+      <c r="C93" t="s">
+        <v>300</v>
+      </c>
+      <c r="D93" t="s">
+        <v>234</v>
+      </c>
+      <c r="E93" t="s">
+        <v>355</v>
+      </c>
+      <c r="F93" t="s">
+        <v>302</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>697</v>
+      </c>
+      <c r="B94" t="s">
+        <v>698</v>
+      </c>
+      <c r="C94" t="s">
+        <v>699</v>
+      </c>
+      <c r="D94" t="s">
+        <v>253</v>
+      </c>
+      <c r="E94" t="s">
+        <v>700</v>
+      </c>
+      <c r="F94" t="s">
+        <v>701</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>703</v>
+      </c>
+      <c r="B95" t="s">
+        <v>704</v>
+      </c>
+      <c r="C95" t="s">
+        <v>294</v>
+      </c>
+      <c r="D95" t="s">
+        <v>234</v>
+      </c>
+      <c r="E95" t="s">
+        <v>705</v>
+      </c>
+      <c r="F95" t="s">
+        <v>507</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>707</v>
+      </c>
+      <c r="B96" t="s">
+        <v>435</v>
+      </c>
+      <c r="C96" t="s">
+        <v>436</v>
+      </c>
+      <c r="D96" t="s">
+        <v>234</v>
+      </c>
+      <c r="E96" t="s">
+        <v>708</v>
+      </c>
+      <c r="F96" t="s">
+        <v>438</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>710</v>
+      </c>
+      <c r="B97" t="s">
+        <v>711</v>
+      </c>
+      <c r="C97" t="s">
+        <v>712</v>
+      </c>
+      <c r="D97" t="s">
+        <v>234</v>
+      </c>
+      <c r="E97" t="s">
+        <v>713</v>
+      </c>
+      <c r="F97" t="s">
+        <v>426</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>715</v>
+      </c>
+      <c r="B98" t="s">
+        <v>388</v>
+      </c>
+      <c r="C98" t="s">
+        <v>716</v>
+      </c>
+      <c r="D98" t="s">
+        <v>360</v>
+      </c>
+      <c r="E98" t="s">
+        <v>228</v>
+      </c>
+      <c r="F98" t="s">
+        <v>717</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>719</v>
+      </c>
+      <c r="B99" t="s">
+        <v>720</v>
+      </c>
+      <c r="C99" t="s">
+        <v>663</v>
+      </c>
+      <c r="D99" t="s">
+        <v>234</v>
+      </c>
+      <c r="E99" t="s">
+        <v>721</v>
+      </c>
+      <c r="F99" t="s">
+        <v>722</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>724</v>
+      </c>
+      <c r="B100" t="s">
+        <v>245</v>
+      </c>
+      <c r="C100" t="s">
+        <v>246</v>
+      </c>
+      <c r="D100" t="s">
+        <v>234</v>
+      </c>
+      <c r="E100" t="s">
+        <v>475</v>
+      </c>
+      <c r="F100" t="s">
+        <v>248</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>726</v>
+      </c>
+      <c r="B101" t="s">
+        <v>727</v>
+      </c>
+      <c r="C101" t="s">
+        <v>728</v>
+      </c>
+      <c r="D101" t="s">
+        <v>360</v>
+      </c>
+      <c r="E101" t="s">
+        <v>700</v>
+      </c>
+      <c r="F101" t="s">
+        <v>729</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>731</v>
+      </c>
+      <c r="B102" t="s">
+        <v>732</v>
+      </c>
+      <c r="C102" t="s">
+        <v>733</v>
+      </c>
+      <c r="D102" t="s">
+        <v>234</v>
+      </c>
+      <c r="E102" t="s">
+        <v>734</v>
+      </c>
+      <c r="F102" t="s">
+        <v>693</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>736</v>
+      </c>
+      <c r="B103" t="s">
+        <v>737</v>
+      </c>
+      <c r="C103" t="s">
+        <v>383</v>
+      </c>
+      <c r="D103" t="s">
+        <v>234</v>
+      </c>
+      <c r="E103" t="s">
+        <v>738</v>
+      </c>
+      <c r="F103" t="s">
+        <v>523</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>740</v>
+      </c>
+      <c r="B104" t="s">
+        <v>737</v>
+      </c>
+      <c r="C104" t="s">
+        <v>383</v>
+      </c>
+      <c r="D104" t="s">
+        <v>234</v>
+      </c>
+      <c r="E104" t="s">
+        <v>738</v>
+      </c>
+      <c r="F104" t="s">
+        <v>523</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>742</v>
+      </c>
+      <c r="B105" t="s">
+        <v>743</v>
+      </c>
+      <c r="C105" t="s">
+        <v>383</v>
+      </c>
+      <c r="D105" t="s">
+        <v>234</v>
+      </c>
+      <c r="E105" t="s">
+        <v>744</v>
+      </c>
+      <c r="F105" t="s">
+        <v>228</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>742</v>
+      </c>
+      <c r="B106" t="s">
+        <v>743</v>
+      </c>
+      <c r="C106" t="s">
+        <v>458</v>
+      </c>
+      <c r="D106" t="s">
+        <v>234</v>
+      </c>
+      <c r="E106" t="s">
+        <v>744</v>
+      </c>
+      <c r="F106" t="s">
+        <v>228</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>747</v>
+      </c>
+      <c r="B107" t="s">
+        <v>748</v>
+      </c>
+      <c r="C107" t="s">
+        <v>749</v>
+      </c>
+      <c r="D107" t="s">
+        <v>234</v>
+      </c>
+      <c r="E107" t="s">
+        <v>750</v>
+      </c>
+      <c r="F107" t="s">
+        <v>751</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>753</v>
+      </c>
+      <c r="B108" t="s">
+        <v>754</v>
+      </c>
+      <c r="C108" t="s">
+        <v>413</v>
+      </c>
+      <c r="D108" t="s">
+        <v>622</v>
+      </c>
+      <c r="E108" t="s">
+        <v>378</v>
+      </c>
+      <c r="F108" t="s">
+        <v>755</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>757</v>
+      </c>
+      <c r="B109" t="s">
+        <v>758</v>
+      </c>
+      <c r="C109" t="s">
+        <v>759</v>
+      </c>
+      <c r="D109" t="s">
+        <v>234</v>
+      </c>
+      <c r="E109" t="s">
+        <v>760</v>
+      </c>
+      <c r="F109" t="s">
+        <v>761</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>763</v>
+      </c>
+      <c r="B110" t="s">
+        <v>764</v>
+      </c>
+      <c r="C110" t="s">
+        <v>418</v>
+      </c>
+      <c r="D110" t="s">
+        <v>234</v>
+      </c>
+      <c r="E110" t="s">
+        <v>765</v>
+      </c>
+      <c r="F110" t="s">
+        <v>766</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>768</v>
+      </c>
+      <c r="B111" t="s">
+        <v>504</v>
+      </c>
+      <c r="C111" t="s">
+        <v>769</v>
+      </c>
+      <c r="D111" t="s">
+        <v>234</v>
+      </c>
+      <c r="E111" t="s">
+        <v>770</v>
+      </c>
+      <c r="F111" t="s">
+        <v>507</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>772</v>
+      </c>
+      <c r="B112" t="s">
+        <v>773</v>
+      </c>
+      <c r="C112" t="s">
+        <v>246</v>
+      </c>
+      <c r="D112" t="s">
+        <v>622</v>
+      </c>
+      <c r="E112" t="s">
+        <v>774</v>
+      </c>
+      <c r="F112" t="s">
+        <v>775</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>777</v>
+      </c>
+      <c r="B113" t="s">
+        <v>778</v>
+      </c>
+      <c r="C113" t="s">
+        <v>246</v>
+      </c>
+      <c r="D113" t="s">
+        <v>234</v>
+      </c>
+      <c r="E113" t="s">
+        <v>779</v>
+      </c>
+      <c r="F113" t="s">
+        <v>751</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>781</v>
+      </c>
+      <c r="B114" t="s">
+        <v>782</v>
+      </c>
+      <c r="C114" t="s">
+        <v>383</v>
+      </c>
+      <c r="D114" t="s">
+        <v>234</v>
+      </c>
+      <c r="E114" t="s">
+        <v>783</v>
+      </c>
+      <c r="F114" t="s">
+        <v>784</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>786</v>
+      </c>
+      <c r="B115" t="s">
+        <v>787</v>
+      </c>
+      <c r="C115" t="s">
+        <v>246</v>
+      </c>
+      <c r="D115" t="s">
+        <v>234</v>
+      </c>
+      <c r="E115" t="s">
+        <v>788</v>
+      </c>
+      <c r="F115" t="s">
+        <v>789</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>791</v>
+      </c>
+      <c r="B116" t="s">
+        <v>662</v>
+      </c>
+      <c r="C116" t="s">
+        <v>663</v>
+      </c>
+      <c r="D116" t="s">
+        <v>234</v>
+      </c>
+      <c r="E116" t="s">
+        <v>792</v>
+      </c>
+      <c r="F116" t="s">
+        <v>665</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>794</v>
+      </c>
+      <c r="B117" t="s">
+        <v>795</v>
+      </c>
+      <c r="C117" t="s">
+        <v>383</v>
+      </c>
+      <c r="D117" t="s">
+        <v>234</v>
+      </c>
+      <c r="E117" t="s">
+        <v>796</v>
+      </c>
+      <c r="F117" t="s">
+        <v>797</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>799</v>
+      </c>
+      <c r="B118" t="s">
+        <v>800</v>
+      </c>
+      <c r="C118" t="s">
+        <v>246</v>
+      </c>
+      <c r="D118" t="s">
+        <v>234</v>
+      </c>
+      <c r="E118" t="s">
+        <v>228</v>
+      </c>
+      <c r="F118" t="s">
+        <v>228</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>802</v>
+      </c>
+      <c r="B119" t="s">
+        <v>803</v>
+      </c>
+      <c r="C119" t="s">
+        <v>246</v>
+      </c>
+      <c r="D119" t="s">
+        <v>234</v>
+      </c>
+      <c r="E119" t="s">
+        <v>804</v>
+      </c>
+      <c r="F119" t="s">
+        <v>805</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>807</v>
+      </c>
+      <c r="B120" t="s">
+        <v>808</v>
+      </c>
+      <c r="C120" t="s">
+        <v>809</v>
+      </c>
+      <c r="D120" t="s">
+        <v>234</v>
+      </c>
+      <c r="E120" t="s">
+        <v>810</v>
+      </c>
+      <c r="F120" t="s">
+        <v>352</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>812</v>
+      </c>
+      <c r="B121" t="s">
+        <v>813</v>
+      </c>
+      <c r="C121" t="s">
+        <v>383</v>
+      </c>
+      <c r="D121" t="s">
+        <v>234</v>
+      </c>
+      <c r="E121" t="s">
+        <v>814</v>
+      </c>
+      <c r="F121" t="s">
+        <v>815</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>817</v>
+      </c>
+      <c r="B122" t="s">
+        <v>800</v>
+      </c>
+      <c r="C122" t="s">
+        <v>246</v>
+      </c>
+      <c r="D122" t="s">
+        <v>234</v>
+      </c>
+      <c r="E122" t="s">
+        <v>228</v>
+      </c>
+      <c r="F122" t="s">
+        <v>228</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>819</v>
+      </c>
+      <c r="B123" t="s">
+        <v>803</v>
+      </c>
+      <c r="C123" t="s">
+        <v>246</v>
+      </c>
+      <c r="D123" t="s">
+        <v>234</v>
+      </c>
+      <c r="E123" t="s">
+        <v>820</v>
+      </c>
+      <c r="F123" t="s">
+        <v>805</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>822</v>
+      </c>
+      <c r="B124" t="s">
+        <v>823</v>
+      </c>
+      <c r="C124" t="s">
+        <v>824</v>
+      </c>
+      <c r="D124" t="s">
+        <v>234</v>
+      </c>
+      <c r="E124" t="s">
+        <v>825</v>
+      </c>
+      <c r="F124" t="s">
+        <v>826</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>828</v>
+      </c>
+      <c r="B125" t="s">
+        <v>829</v>
+      </c>
+      <c r="C125" t="s">
+        <v>418</v>
+      </c>
+      <c r="D125" t="s">
+        <v>234</v>
+      </c>
+      <c r="E125" t="s">
+        <v>830</v>
+      </c>
+      <c r="F125" t="s">
+        <v>831</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>833</v>
+      </c>
+      <c r="B126" t="s">
+        <v>834</v>
+      </c>
+      <c r="C126" t="s">
+        <v>835</v>
+      </c>
+      <c r="D126" t="s">
+        <v>360</v>
+      </c>
+      <c r="E126" t="s">
+        <v>836</v>
+      </c>
+      <c r="F126" t="s">
+        <v>507</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>838</v>
+      </c>
+      <c r="B127" t="s">
+        <v>839</v>
+      </c>
+      <c r="C127" t="s">
+        <v>282</v>
+      </c>
+      <c r="D127" t="s">
+        <v>622</v>
+      </c>
+      <c r="E127" t="s">
+        <v>840</v>
+      </c>
+      <c r="F127" t="s">
+        <v>841</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>843</v>
+      </c>
+      <c r="B128" t="s">
+        <v>839</v>
+      </c>
+      <c r="C128" t="s">
+        <v>282</v>
+      </c>
+      <c r="D128" t="s">
+        <v>622</v>
+      </c>
+      <c r="E128" t="s">
+        <v>840</v>
+      </c>
+      <c r="F128" t="s">
+        <v>751</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>845</v>
+      </c>
+      <c r="B129" t="s">
+        <v>846</v>
+      </c>
+      <c r="C129" t="s">
+        <v>282</v>
+      </c>
+      <c r="D129" t="s">
+        <v>234</v>
+      </c>
+      <c r="E129" t="s">
+        <v>847</v>
+      </c>
+      <c r="F129" t="s">
+        <v>848</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>850</v>
+      </c>
+      <c r="B130" t="s">
+        <v>851</v>
+      </c>
+      <c r="C130" t="s">
+        <v>383</v>
+      </c>
+      <c r="D130" t="s">
+        <v>234</v>
+      </c>
+      <c r="E130" t="s">
+        <v>852</v>
+      </c>
+      <c r="F130" t="s">
+        <v>853</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>855</v>
+      </c>
+      <c r="B131" t="s">
+        <v>856</v>
+      </c>
+      <c r="C131" t="s">
+        <v>233</v>
+      </c>
+      <c r="D131" t="s">
+        <v>234</v>
+      </c>
+      <c r="E131" t="s">
+        <v>228</v>
+      </c>
+      <c r="F131" t="s">
+        <v>857</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -5065,6 +7212,64 @@
     <hyperlink ref="H71" r:id="rId70"/>
     <hyperlink ref="H72" r:id="rId71"/>
     <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
